--- a/research/traditional_assets/database/data/germany/germany_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_coal_related_energy.xlsx
@@ -1133,13 +1133,13 @@
         <v>24.9971061093248</v>
       </c>
       <c r="F2">
-        <v>4.50001696615927</v>
+        <v>4.50001696615926</v>
       </c>
       <c r="G2">
         <v>0.933487003366179</v>
       </c>
       <c r="H2">
-        <v>3.09181289751814</v>
+        <v>3.09181289751815</v>
       </c>
       <c r="I2">
         <v>0.175114885634572</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09273596451495866</v>
+        <v>0.09248925662141377</v>
       </c>
       <c r="C2">
-        <v>526.9128104216002</v>
+        <v>522.2881544380158</v>
       </c>
       <c r="D2">
-        <v>474.2128104216001</v>
+        <v>474.974359041087</v>
       </c>
       <c r="E2">
-        <v>-94.32046030712212</v>
+        <v>-88.9342557040509</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.386204603071222</v>
       </c>
       <c r="G2">
         <v>52.7</v>
@@ -1451,28 +1451,28 @@
         <v>77.741</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2709260915344824</v>
       </c>
       <c r="N2">
-        <v>77.741</v>
+        <v>77.47007390846552</v>
       </c>
       <c r="O2">
-        <v>23.3223</v>
+        <v>23.24102217253965</v>
       </c>
       <c r="P2">
-        <v>54.4187</v>
+        <v>54.22905173592586</v>
       </c>
       <c r="Q2">
-        <v>77.7187</v>
+        <v>77.52905173592586</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09273596451495866</v>
+        <v>0.09306783497112503</v>
       </c>
       <c r="T2">
-        <v>1.083971466858168</v>
+        <v>1.091635911573327</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>286.9454158500841</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09248925662141377</v>
+        <v>0.09224254872786893</v>
       </c>
       <c r="C3">
-        <v>522.2881544380158</v>
+        <v>517.6659483636263</v>
       </c>
       <c r="D3">
-        <v>474.974359041087</v>
+        <v>475.7383575697688</v>
       </c>
       <c r="E3">
-        <v>-88.9342557040509</v>
+        <v>-83.54805110097968</v>
       </c>
       <c r="F3">
-        <v>5.386204603071222</v>
+        <v>10.77240920614244</v>
       </c>
       <c r="G3">
         <v>52.7</v>
@@ -1533,28 +1533,28 @@
         <v>77.741</v>
       </c>
       <c r="M3">
-        <v>0.2709260915344824</v>
+        <v>0.5418521830689649</v>
       </c>
       <c r="N3">
-        <v>77.47007390846552</v>
+        <v>77.19914781693103</v>
       </c>
       <c r="O3">
-        <v>23.24102217253965</v>
+        <v>23.15974434507931</v>
       </c>
       <c r="P3">
-        <v>54.22905173592586</v>
+        <v>54.03940347185173</v>
       </c>
       <c r="Q3">
-        <v>77.52905173592586</v>
+        <v>77.33940347185172</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09306783497112503</v>
+        <v>0.09340647829374379</v>
       </c>
       <c r="T3">
-        <v>1.091635911573327</v>
+        <v>1.09945677352757</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>286.9454158500841</v>
+        <v>143.472707925042</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09224254872786893</v>
+        <v>0.09199584083432404</v>
       </c>
       <c r="C4">
-        <v>517.6659483636263</v>
+        <v>513.0462040395506</v>
       </c>
       <c r="D4">
-        <v>475.7383575697688</v>
+        <v>476.5048178487642</v>
       </c>
       <c r="E4">
-        <v>-83.54805110097968</v>
+        <v>-78.16184649790846</v>
       </c>
       <c r="F4">
-        <v>10.77240920614244</v>
+        <v>16.15861380921366</v>
       </c>
       <c r="G4">
         <v>52.7</v>
@@ -1615,28 +1615,28 @@
         <v>77.741</v>
       </c>
       <c r="M4">
-        <v>0.5418521830689649</v>
+        <v>0.8127782746034472</v>
       </c>
       <c r="N4">
-        <v>77.19914781693103</v>
+        <v>76.92822172539655</v>
       </c>
       <c r="O4">
-        <v>23.15974434507931</v>
+        <v>23.07846651761897</v>
       </c>
       <c r="P4">
-        <v>54.03940347185173</v>
+        <v>53.84975520777759</v>
       </c>
       <c r="Q4">
-        <v>77.33940347185172</v>
+        <v>77.14975520777759</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09340647829374379</v>
+        <v>0.09375210395291138</v>
       </c>
       <c r="T4">
-        <v>1.09945677352757</v>
+        <v>1.107438890367469</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>143.472707925042</v>
+        <v>95.64847195002804</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09199584083432404</v>
+        <v>0.09174913294077915</v>
       </c>
       <c r="C5">
-        <v>513.0462040395506</v>
+        <v>508.4289333833386</v>
       </c>
       <c r="D5">
-        <v>476.5048178487642</v>
+        <v>477.2737517956235</v>
       </c>
       <c r="E5">
-        <v>-78.16184649790846</v>
+        <v>-72.77564189483724</v>
       </c>
       <c r="F5">
-        <v>16.15861380921366</v>
+        <v>21.54481841228489</v>
       </c>
       <c r="G5">
         <v>52.7</v>
@@ -1697,28 +1697,28 @@
         <v>77.741</v>
       </c>
       <c r="M5">
-        <v>0.8127782746034472</v>
+        <v>1.08370436613793</v>
       </c>
       <c r="N5">
-        <v>76.92822172539655</v>
+        <v>76.65729563386208</v>
       </c>
       <c r="O5">
-        <v>23.07846651761897</v>
+        <v>22.99718869015862</v>
       </c>
       <c r="P5">
-        <v>53.84975520777759</v>
+        <v>53.66010694370345</v>
       </c>
       <c r="Q5">
-        <v>77.14975520777759</v>
+        <v>76.96010694370345</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09375210395291138</v>
+        <v>0.09410493014664495</v>
       </c>
       <c r="T5">
-        <v>1.107438890367469</v>
+        <v>1.115587301308198</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>95.64847195002804</v>
+        <v>71.73635396252102</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09174913294077915</v>
+        <v>0.09150242504723427</v>
       </c>
       <c r="C6">
-        <v>508.4289333833386</v>
+        <v>503.8141483895903</v>
       </c>
       <c r="D6">
-        <v>477.2737517956235</v>
+        <v>478.0451714049464</v>
       </c>
       <c r="E6">
-        <v>-72.77564189483724</v>
+        <v>-67.38943729176601</v>
       </c>
       <c r="F6">
-        <v>21.54481841228489</v>
+        <v>26.93102301535611</v>
       </c>
       <c r="G6">
         <v>52.7</v>
@@ -1779,28 +1779,28 @@
         <v>77.741</v>
       </c>
       <c r="M6">
-        <v>1.08370436613793</v>
+        <v>1.354630457672412</v>
       </c>
       <c r="N6">
-        <v>76.65729563386208</v>
+        <v>76.38636954232759</v>
       </c>
       <c r="O6">
-        <v>22.99718869015862</v>
+        <v>22.91591086269828</v>
       </c>
       <c r="P6">
-        <v>53.66010694370345</v>
+        <v>53.47045867962931</v>
       </c>
       <c r="Q6">
-        <v>76.96010694370345</v>
+        <v>76.77045867962931</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09410493014664495</v>
+        <v>0.09446518426024661</v>
       </c>
       <c r="T6">
-        <v>1.115587301308198</v>
+        <v>1.123907257742416</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>71.73635396252102</v>
+        <v>57.38908317001681</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09150242504723427</v>
+        <v>0.09125571715368941</v>
       </c>
       <c r="C7">
-        <v>503.8141483895903</v>
+        <v>499.2018611305788</v>
       </c>
       <c r="D7">
-        <v>478.0451714049464</v>
+        <v>478.8190887490062</v>
       </c>
       <c r="E7">
-        <v>-67.38943729176601</v>
+        <v>-62.00323268869479</v>
       </c>
       <c r="F7">
-        <v>26.93102301535611</v>
+        <v>32.31722761842733</v>
       </c>
       <c r="G7">
         <v>52.7</v>
@@ -1861,28 +1861,28 @@
         <v>77.741</v>
       </c>
       <c r="M7">
-        <v>1.354630457672412</v>
+        <v>1.625556549206895</v>
       </c>
       <c r="N7">
-        <v>76.38636954232759</v>
+        <v>76.11544345079311</v>
       </c>
       <c r="O7">
-        <v>22.91591086269828</v>
+        <v>22.83463303523793</v>
       </c>
       <c r="P7">
-        <v>53.47045867962931</v>
+        <v>53.28081041555518</v>
       </c>
       <c r="Q7">
-        <v>76.77045867962931</v>
+        <v>76.58081041555518</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09446518426024661</v>
+        <v>0.09483310335498873</v>
       </c>
       <c r="T7">
-        <v>1.123907257742416</v>
+        <v>1.132404234526299</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.38908317001681</v>
+        <v>47.82423597501401</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09125571715368941</v>
+        <v>0.09100900926014455</v>
       </c>
       <c r="C8">
-        <v>499.2018611305789</v>
+        <v>494.5920837568804</v>
       </c>
       <c r="D8">
-        <v>478.8190887490062</v>
+        <v>479.595515978379</v>
       </c>
       <c r="E8">
-        <v>-62.00323268869479</v>
+        <v>-56.61702808562357</v>
       </c>
       <c r="F8">
-        <v>32.31722761842732</v>
+        <v>37.70343222149855</v>
       </c>
       <c r="G8">
         <v>52.7</v>
@@ -1943,28 +1943,28 @@
         <v>77.741</v>
       </c>
       <c r="M8">
-        <v>1.625556549206894</v>
+        <v>1.896482640741377</v>
       </c>
       <c r="N8">
-        <v>76.11544345079311</v>
+        <v>75.84451735925862</v>
       </c>
       <c r="O8">
-        <v>22.83463303523793</v>
+        <v>22.75335520777758</v>
       </c>
       <c r="P8">
-        <v>53.28081041555518</v>
+        <v>53.09116215148103</v>
       </c>
       <c r="Q8">
-        <v>76.58081041555518</v>
+        <v>76.39116215148103</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09483310335498873</v>
+        <v>0.09520893468832746</v>
       </c>
       <c r="T8">
-        <v>1.132404234526299</v>
+        <v>1.141083941993706</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>47.82423597501402</v>
+        <v>40.99220226429773</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09100900926014453</v>
+        <v>0.09076230136659967</v>
       </c>
       <c r="C9">
-        <v>494.5920837568804</v>
+        <v>489.98482849801</v>
       </c>
       <c r="D9">
-        <v>479.595515978379</v>
+        <v>480.3744653225797</v>
       </c>
       <c r="E9">
-        <v>-56.61702808562357</v>
+        <v>-51.23082348255235</v>
       </c>
       <c r="F9">
-        <v>37.70343222149855</v>
+        <v>43.08963682456977</v>
       </c>
       <c r="G9">
         <v>52.7</v>
@@ -2025,28 +2025,28 @@
         <v>77.741</v>
       </c>
       <c r="M9">
-        <v>1.896482640741377</v>
+        <v>2.16740873227586</v>
       </c>
       <c r="N9">
-        <v>75.84451735925862</v>
+        <v>75.57359126772414</v>
       </c>
       <c r="O9">
-        <v>22.75335520777758</v>
+        <v>22.67207738031724</v>
       </c>
       <c r="P9">
-        <v>53.09116215148103</v>
+        <v>52.9015138874069</v>
       </c>
       <c r="Q9">
-        <v>76.39116215148103</v>
+        <v>76.2015138874069</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09520893468832746</v>
+        <v>0.09559293626804312</v>
       </c>
       <c r="T9">
-        <v>1.141083941993706</v>
+        <v>1.149952338753883</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>40.99220226429772</v>
+        <v>35.8681769812605</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09076230136659967</v>
+        <v>0.0905155934730548</v>
       </c>
       <c r="C10">
-        <v>489.98482849801</v>
+        <v>485.3801076630635</v>
       </c>
       <c r="D10">
-        <v>480.3744653225797</v>
+        <v>481.1559490907044</v>
       </c>
       <c r="E10">
-        <v>-51.23082348255235</v>
+        <v>-45.84461887948113</v>
       </c>
       <c r="F10">
-        <v>43.08963682456977</v>
+        <v>48.47584142764099</v>
       </c>
       <c r="G10">
         <v>52.7</v>
@@ -2107,28 +2107,28 @@
         <v>77.741</v>
       </c>
       <c r="M10">
-        <v>2.16740873227586</v>
+        <v>2.438334823810342</v>
       </c>
       <c r="N10">
-        <v>75.57359126772414</v>
+        <v>75.30266517618966</v>
       </c>
       <c r="O10">
-        <v>22.67207738031724</v>
+        <v>22.5907995528569</v>
       </c>
       <c r="P10">
-        <v>52.9015138874069</v>
+        <v>52.71186562333277</v>
       </c>
       <c r="Q10">
-        <v>76.2015138874069</v>
+        <v>76.01186562333277</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09559293626804312</v>
+        <v>0.09598537744291735</v>
       </c>
       <c r="T10">
-        <v>1.149952338753883</v>
+        <v>1.159015645332964</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>35.8681769812605</v>
+        <v>31.88282398334268</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0905155934730548</v>
+        <v>0.09026888557950991</v>
       </c>
       <c r="C11">
-        <v>485.3801076630635</v>
+        <v>480.7779336413663</v>
       </c>
       <c r="D11">
-        <v>481.1559490907044</v>
+        <v>481.9399796720785</v>
       </c>
       <c r="E11">
-        <v>-45.84461887948113</v>
+        <v>-40.45841427640991</v>
       </c>
       <c r="F11">
-        <v>48.47584142764099</v>
+        <v>53.86204603071221</v>
       </c>
       <c r="G11">
         <v>52.7</v>
@@ -2189,28 +2189,28 @@
         <v>77.741</v>
       </c>
       <c r="M11">
-        <v>2.438334823810342</v>
+        <v>2.709260915344824</v>
       </c>
       <c r="N11">
-        <v>75.30266517618966</v>
+        <v>75.03173908465517</v>
       </c>
       <c r="O11">
-        <v>22.5907995528569</v>
+        <v>22.50952172539655</v>
       </c>
       <c r="P11">
-        <v>52.71186562333277</v>
+        <v>52.52221735925862</v>
       </c>
       <c r="Q11">
-        <v>76.01186562333277</v>
+        <v>75.82221735925862</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09598537744291735</v>
+        <v>0.09638653953278878</v>
       </c>
       <c r="T11">
-        <v>1.159015645332964</v>
+        <v>1.168280358724914</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.88282398334268</v>
+        <v>28.69454158500841</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09026888557950991</v>
+        <v>0.09002217768596503</v>
       </c>
       <c r="C12">
-        <v>480.7779336413663</v>
+        <v>476.1783189031278</v>
       </c>
       <c r="D12">
-        <v>481.9399796720785</v>
+        <v>482.7265695369111</v>
       </c>
       <c r="E12">
-        <v>-40.4584142764099</v>
+        <v>-35.07220967333868</v>
       </c>
       <c r="F12">
-        <v>53.86204603071221</v>
+        <v>59.24825063378344</v>
       </c>
       <c r="G12">
         <v>52.7</v>
@@ -2271,28 +2271,28 @@
         <v>77.741</v>
       </c>
       <c r="M12">
-        <v>2.709260915344824</v>
+        <v>2.980187006879307</v>
       </c>
       <c r="N12">
-        <v>75.03173908465517</v>
+        <v>74.76081299312069</v>
       </c>
       <c r="O12">
-        <v>22.50952172539655</v>
+        <v>22.42824389793621</v>
       </c>
       <c r="P12">
-        <v>52.52221735925862</v>
+        <v>52.33256909518448</v>
       </c>
       <c r="Q12">
-        <v>75.82221735925862</v>
+        <v>75.63256909518448</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09638653953278878</v>
+        <v>0.0967967165010843</v>
       </c>
       <c r="T12">
-        <v>1.168280358724914</v>
+        <v>1.177753267923425</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.69454158500841</v>
+        <v>26.08594689546219</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09002217768596503</v>
+        <v>0.08977546979242017</v>
       </c>
       <c r="C13">
-        <v>476.1783189031278</v>
+        <v>471.5812760001025</v>
       </c>
       <c r="D13">
-        <v>482.7265695369111</v>
+        <v>483.5157312369571</v>
       </c>
       <c r="E13">
-        <v>-35.07220967333868</v>
+        <v>-29.68600507026747</v>
       </c>
       <c r="F13">
-        <v>59.24825063378344</v>
+        <v>64.63445523685465</v>
       </c>
       <c r="G13">
         <v>52.7</v>
@@ -2353,28 +2353,28 @@
         <v>77.741</v>
       </c>
       <c r="M13">
-        <v>2.980187006879307</v>
+        <v>3.251113098413789</v>
       </c>
       <c r="N13">
-        <v>74.76081299312069</v>
+        <v>74.48988690158622</v>
       </c>
       <c r="O13">
-        <v>22.42824389793621</v>
+        <v>22.34696607047587</v>
       </c>
       <c r="P13">
-        <v>52.33256909518448</v>
+        <v>52.14292083111035</v>
       </c>
       <c r="Q13">
-        <v>75.63256909518448</v>
+        <v>75.44292083111036</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0967967165010843</v>
+        <v>0.09721621567320474</v>
       </c>
       <c r="T13">
-        <v>1.177753267923425</v>
+        <v>1.187441470512812</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.08594689546219</v>
+        <v>23.91211798750701</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08977546979242017</v>
+        <v>0.08952876189887529</v>
       </c>
       <c r="C14">
-        <v>471.5812760001025</v>
+        <v>466.9868175662581</v>
       </c>
       <c r="D14">
-        <v>483.5157312369571</v>
+        <v>484.3074774061839</v>
       </c>
       <c r="E14">
-        <v>-29.68600507026747</v>
+        <v>-24.29980046719623</v>
       </c>
       <c r="F14">
-        <v>64.63445523685465</v>
+        <v>70.02065983992588</v>
       </c>
       <c r="G14">
         <v>52.7</v>
@@ -2435,28 +2435,28 @@
         <v>77.741</v>
       </c>
       <c r="M14">
-        <v>3.251113098413789</v>
+        <v>3.522039189948272</v>
       </c>
       <c r="N14">
-        <v>74.48988690158622</v>
+        <v>74.21896081005173</v>
       </c>
       <c r="O14">
-        <v>22.34696607047587</v>
+        <v>22.26568824301552</v>
       </c>
       <c r="P14">
-        <v>52.14292083111035</v>
+        <v>51.95327256703621</v>
       </c>
       <c r="Q14">
-        <v>75.44292083111036</v>
+        <v>75.25327256703621</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09721621567320474</v>
+        <v>0.09764535850445435</v>
       </c>
       <c r="T14">
-        <v>1.187441470512812</v>
+        <v>1.197352390403103</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.91211798750701</v>
+        <v>22.07272429616031</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08952876189887529</v>
+        <v>0.08928205400533042</v>
       </c>
       <c r="C15">
-        <v>466.9868175662581</v>
+        <v>462.394956318449</v>
       </c>
       <c r="D15">
-        <v>484.3074774061839</v>
+        <v>485.1018207614462</v>
       </c>
       <c r="E15">
-        <v>-24.29980046719623</v>
+        <v>-18.91359586412501</v>
       </c>
       <c r="F15">
-        <v>70.02065983992588</v>
+        <v>75.4068644429971</v>
       </c>
       <c r="G15">
         <v>52.7</v>
@@ -2517,28 +2517,28 @@
         <v>77.741</v>
       </c>
       <c r="M15">
-        <v>3.522039189948272</v>
+        <v>3.792965281482754</v>
       </c>
       <c r="N15">
-        <v>74.21896081005173</v>
+        <v>73.94803471851725</v>
       </c>
       <c r="O15">
-        <v>22.26568824301552</v>
+        <v>22.18441041555517</v>
       </c>
       <c r="P15">
-        <v>51.95327256703621</v>
+        <v>51.76362430296207</v>
       </c>
       <c r="Q15">
-        <v>75.25327256703621</v>
+        <v>75.06362430296207</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09764535850445435</v>
+        <v>0.09808448140154699</v>
       </c>
       <c r="T15">
-        <v>1.197352390403103</v>
+        <v>1.207493796802471</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.07272429616031</v>
+        <v>20.49610113214886</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08928205400533042</v>
+        <v>0.08903534611178553</v>
       </c>
       <c r="C16">
-        <v>462.394956318449</v>
+        <v>457.805705057098</v>
       </c>
       <c r="D16">
-        <v>485.1018207614462</v>
+        <v>485.8987741031663</v>
       </c>
       <c r="E16">
-        <v>-18.91359586412501</v>
+        <v>-13.52739126105379</v>
       </c>
       <c r="F16">
-        <v>75.4068644429971</v>
+        <v>80.79306904606833</v>
       </c>
       <c r="G16">
         <v>52.7</v>
@@ -2599,28 +2599,28 @@
         <v>77.741</v>
       </c>
       <c r="M16">
-        <v>3.792965281482754</v>
+        <v>4.063891373017237</v>
       </c>
       <c r="N16">
-        <v>73.94803471851725</v>
+        <v>73.67710862698276</v>
       </c>
       <c r="O16">
-        <v>22.18441041555517</v>
+        <v>22.10313258809483</v>
       </c>
       <c r="P16">
-        <v>51.76362430296207</v>
+        <v>51.57397603888793</v>
       </c>
       <c r="Q16">
-        <v>75.06362430296207</v>
+        <v>74.87397603888793</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09808448140154699</v>
+        <v>0.09853393660210062</v>
       </c>
       <c r="T16">
-        <v>1.207493796802471</v>
+        <v>1.217873824528883</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.49610113214886</v>
+        <v>19.1296943900056</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08903534611178553</v>
+        <v>0.08878863821824065</v>
       </c>
       <c r="C17">
-        <v>457.805705057098</v>
+        <v>453.219076666883</v>
       </c>
       <c r="D17">
-        <v>485.8987741031663</v>
+        <v>486.6983503160225</v>
       </c>
       <c r="E17">
-        <v>-13.52739126105381</v>
+        <v>-8.141186657982573</v>
       </c>
       <c r="F17">
-        <v>80.79306904606831</v>
+        <v>86.17927364913955</v>
       </c>
       <c r="G17">
         <v>52.7</v>
@@ -2681,28 +2681,28 @@
         <v>77.741</v>
       </c>
       <c r="M17">
-        <v>4.063891373017236</v>
+        <v>4.334817464551719</v>
       </c>
       <c r="N17">
-        <v>73.67710862698276</v>
+        <v>73.40618253544828</v>
       </c>
       <c r="O17">
-        <v>22.10313258809483</v>
+        <v>22.02185476063448</v>
       </c>
       <c r="P17">
-        <v>51.57397603888793</v>
+        <v>51.3843277748138</v>
       </c>
       <c r="Q17">
-        <v>74.87397603888793</v>
+        <v>74.6843277748138</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09853393660210062</v>
+        <v>0.09899409311695316</v>
       </c>
       <c r="T17">
-        <v>1.217873824528883</v>
+        <v>1.228500995772591</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.12969439000561</v>
+        <v>17.93408849063025</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08878863821824065</v>
+        <v>0.08854193032469578</v>
       </c>
       <c r="C18">
-        <v>453.219076666883</v>
+        <v>448.6350841174317</v>
       </c>
       <c r="D18">
-        <v>486.6983503160225</v>
+        <v>487.5005623696425</v>
       </c>
       <c r="E18">
-        <v>-8.141186657982573</v>
+        <v>-2.754982054911352</v>
       </c>
       <c r="F18">
-        <v>86.17927364913955</v>
+        <v>91.56547825221077</v>
       </c>
       <c r="G18">
         <v>52.7</v>
@@ -2763,28 +2763,28 @@
         <v>77.741</v>
       </c>
       <c r="M18">
-        <v>4.334817464551719</v>
+        <v>4.605743556086201</v>
       </c>
       <c r="N18">
-        <v>73.40618253544828</v>
+        <v>73.1352564439138</v>
       </c>
       <c r="O18">
-        <v>22.02185476063448</v>
+        <v>21.94057693317414</v>
       </c>
       <c r="P18">
-        <v>51.3843277748138</v>
+        <v>51.19467951073966</v>
       </c>
       <c r="Q18">
-        <v>74.6843277748138</v>
+        <v>74.49467951073966</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09899409311695316</v>
+        <v>0.09946533774059732</v>
       </c>
       <c r="T18">
-        <v>1.228500995772591</v>
+        <v>1.239384243431809</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.93408849063025</v>
+        <v>16.87914210882847</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08854193032469578</v>
+        <v>0.0882952224311509</v>
       </c>
       <c r="C19">
-        <v>448.6350841174317</v>
+        <v>444.0537404640235</v>
       </c>
       <c r="D19">
-        <v>487.5005623696425</v>
+        <v>488.3054233193054</v>
       </c>
       <c r="E19">
-        <v>-2.754982054911352</v>
+        <v>2.631222548159883</v>
       </c>
       <c r="F19">
-        <v>91.56547825221077</v>
+        <v>96.951682855282</v>
       </c>
       <c r="G19">
         <v>52.7</v>
@@ -2845,28 +2845,28 @@
         <v>77.741</v>
       </c>
       <c r="M19">
-        <v>4.605743556086201</v>
+        <v>4.876669647620685</v>
       </c>
       <c r="N19">
-        <v>73.1352564439138</v>
+        <v>72.86433035237931</v>
       </c>
       <c r="O19">
-        <v>21.94057693317414</v>
+        <v>21.85929910571379</v>
       </c>
       <c r="P19">
-        <v>51.19467951073966</v>
+        <v>51.00503124666552</v>
       </c>
       <c r="Q19">
-        <v>74.49467951073966</v>
+        <v>74.30503124666552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09946533774059732</v>
+        <v>0.09994807613554987</v>
       </c>
       <c r="T19">
-        <v>1.239384243431809</v>
+        <v>1.250532936155887</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.87914210882847</v>
+        <v>15.94141199167133</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08829522243115091</v>
+        <v>0.08804851453760604</v>
       </c>
       <c r="C20">
-        <v>444.0537404640235</v>
+        <v>439.4750588482966</v>
       </c>
       <c r="D20">
-        <v>488.3054233193054</v>
+        <v>489.1129463066498</v>
       </c>
       <c r="E20">
-        <v>2.631222548159855</v>
+        <v>8.01742715123109</v>
       </c>
       <c r="F20">
-        <v>96.95168285528197</v>
+        <v>102.3378874583532</v>
       </c>
       <c r="G20">
         <v>52.7</v>
@@ -2927,28 +2927,28 @@
         <v>77.741</v>
       </c>
       <c r="M20">
-        <v>4.876669647620683</v>
+        <v>5.147595739155166</v>
       </c>
       <c r="N20">
-        <v>72.86433035237931</v>
+        <v>72.59340426084484</v>
       </c>
       <c r="O20">
-        <v>21.85929910571379</v>
+        <v>21.77802127825345</v>
       </c>
       <c r="P20">
-        <v>51.00503124666552</v>
+        <v>50.81538298259139</v>
       </c>
       <c r="Q20">
-        <v>74.30503124666552</v>
+        <v>74.11538298259138</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09994807613554987</v>
+        <v>0.1004427339970445</v>
       </c>
       <c r="T20">
-        <v>1.250532936155887</v>
+        <v>1.261956905243522</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.94141199167134</v>
+        <v>15.10239030789916</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08804851453760604</v>
+        <v>0.08780180664406115</v>
       </c>
       <c r="C21">
-        <v>439.4750588482966</v>
+        <v>434.8990524989644</v>
       </c>
       <c r="D21">
-        <v>489.1129463066498</v>
+        <v>489.9231445603888</v>
       </c>
       <c r="E21">
-        <v>8.01742715123109</v>
+        <v>13.40363175430231</v>
       </c>
       <c r="F21">
-        <v>102.3378874583532</v>
+        <v>107.7240920614244</v>
       </c>
       <c r="G21">
         <v>52.7</v>
@@ -3009,28 +3009,28 @@
         <v>77.741</v>
       </c>
       <c r="M21">
-        <v>5.147595739155166</v>
+        <v>5.418521830689649</v>
       </c>
       <c r="N21">
-        <v>72.59340426084484</v>
+        <v>72.32247816931036</v>
       </c>
       <c r="O21">
-        <v>21.77802127825345</v>
+        <v>21.69674345079311</v>
       </c>
       <c r="P21">
-        <v>50.81538298259139</v>
+        <v>50.62573471851725</v>
       </c>
       <c r="Q21">
-        <v>74.11538298259138</v>
+        <v>73.92573471851725</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1004427339970445</v>
+        <v>0.1009497583050764</v>
       </c>
       <c r="T21">
-        <v>1.261956905243522</v>
+        <v>1.273666473558348</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.10239030789916</v>
+        <v>14.3472707925042</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08780180664406115</v>
+        <v>0.08755509875051627</v>
       </c>
       <c r="C22">
-        <v>434.8990524989644</v>
+        <v>430.3257347325369</v>
       </c>
       <c r="D22">
-        <v>489.9231445603888</v>
+        <v>490.7360313970326</v>
       </c>
       <c r="E22">
-        <v>13.40363175430231</v>
+        <v>18.78983635737355</v>
       </c>
       <c r="F22">
-        <v>107.7240920614244</v>
+        <v>113.1102966644957</v>
       </c>
       <c r="G22">
         <v>52.7</v>
@@ -3091,28 +3091,28 @@
         <v>77.741</v>
       </c>
       <c r="M22">
-        <v>5.418521830689649</v>
+        <v>5.689447922224131</v>
       </c>
       <c r="N22">
-        <v>72.32247816931036</v>
+        <v>72.05155207777587</v>
       </c>
       <c r="O22">
-        <v>21.69674345079311</v>
+        <v>21.61546562333276</v>
       </c>
       <c r="P22">
-        <v>50.62573471851725</v>
+        <v>50.43608645444311</v>
       </c>
       <c r="Q22">
-        <v>73.92573471851725</v>
+        <v>73.73608645444311</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1009497583050764</v>
+        <v>0.1014696186715396</v>
       </c>
       <c r="T22">
-        <v>1.273666473558348</v>
+        <v>1.285672486640637</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.3472707925042</v>
+        <v>13.66406742143257</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08755509875051627</v>
+        <v>0.0873083908569714</v>
       </c>
       <c r="C23">
-        <v>430.3257347325369</v>
+        <v>425.7551189540507</v>
       </c>
       <c r="D23">
-        <v>490.7360313970326</v>
+        <v>491.5516202216176</v>
       </c>
       <c r="E23">
-        <v>18.78983635737353</v>
+        <v>24.17604096044475</v>
       </c>
       <c r="F23">
-        <v>113.1102966644956</v>
+        <v>118.4965012675669</v>
       </c>
       <c r="G23">
         <v>52.7</v>
@@ -3173,28 +3173,28 @@
         <v>77.741</v>
       </c>
       <c r="M23">
-        <v>5.689447922224131</v>
+        <v>5.960374013758614</v>
       </c>
       <c r="N23">
-        <v>72.05155207777587</v>
+        <v>71.78062598624139</v>
       </c>
       <c r="O23">
-        <v>21.61546562333276</v>
+        <v>21.53418779587242</v>
       </c>
       <c r="P23">
-        <v>50.43608645444311</v>
+        <v>50.24643819036898</v>
       </c>
       <c r="Q23">
-        <v>73.73608645444311</v>
+        <v>73.54643819036897</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1014696186715396</v>
+        <v>0.102002808790989</v>
       </c>
       <c r="T23">
-        <v>1.285672486640637</v>
+        <v>1.297986346212217</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.66406742143257</v>
+        <v>13.04297344773109</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0873083908569714</v>
+        <v>0.08730318296342651</v>
       </c>
       <c r="C24">
-        <v>425.7551189540507</v>
+        <v>420.3861602858503</v>
       </c>
       <c r="D24">
-        <v>491.5516202216176</v>
+        <v>491.5688661564884</v>
       </c>
       <c r="E24">
-        <v>24.17604096044475</v>
+        <v>29.56224556351597</v>
       </c>
       <c r="F24">
-        <v>118.4965012675669</v>
+        <v>123.8827058706381</v>
       </c>
       <c r="G24">
         <v>52.7</v>
@@ -3255,45 +3255,45 @@
         <v>77.741</v>
       </c>
       <c r="M24">
-        <v>5.960374013758614</v>
+        <v>6.417124164099053</v>
       </c>
       <c r="N24">
-        <v>71.78062598624139</v>
+        <v>71.32387583590095</v>
       </c>
       <c r="O24">
-        <v>21.53418779587242</v>
+        <v>21.39716275077028</v>
       </c>
       <c r="P24">
-        <v>50.24643819036898</v>
+        <v>49.92671308513066</v>
       </c>
       <c r="Q24">
-        <v>73.54643819036897</v>
+        <v>73.22671308513067</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.102002808790989</v>
+        <v>0.10254984800445</v>
       </c>
       <c r="T24">
-        <v>1.297986346212217</v>
+        <v>1.310620046292149</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.04297344773109</v>
+        <v>12.11461676788587</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08730318296342651</v>
+        <v>0.08706697506988165</v>
       </c>
       <c r="C25">
-        <v>420.3861602858503</v>
+        <v>415.7834320966571</v>
       </c>
       <c r="D25">
-        <v>491.5688661564884</v>
+        <v>492.3523425703663</v>
       </c>
       <c r="E25">
-        <v>29.56224556351597</v>
+        <v>34.94845016658721</v>
       </c>
       <c r="F25">
-        <v>123.8827058706381</v>
+        <v>129.2689104737093</v>
       </c>
       <c r="G25">
         <v>52.7</v>
@@ -3337,28 +3337,28 @@
         <v>77.741</v>
       </c>
       <c r="M25">
-        <v>6.417124164099053</v>
+        <v>6.696129562538143</v>
       </c>
       <c r="N25">
-        <v>71.32387583590095</v>
+        <v>71.04487043746185</v>
       </c>
       <c r="O25">
-        <v>21.39716275077028</v>
+        <v>21.31346113123855</v>
       </c>
       <c r="P25">
-        <v>49.92671308513066</v>
+        <v>49.7314093062233</v>
       </c>
       <c r="Q25">
-        <v>73.22671308513067</v>
+        <v>73.0314093062233</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.10254984800445</v>
+        <v>0.1031112829866864</v>
       </c>
       <c r="T25">
-        <v>1.310620046292149</v>
+        <v>1.323586212163658</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.11461676788587</v>
+        <v>11.60984106922396</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08706697506988165</v>
+        <v>0.08683076717633678</v>
       </c>
       <c r="C26">
-        <v>415.7834320966571</v>
+        <v>411.1832053482315</v>
       </c>
       <c r="D26">
-        <v>492.3523425703663</v>
+        <v>493.1383204250121</v>
       </c>
       <c r="E26">
-        <v>34.94845016658718</v>
+        <v>40.33465476965841</v>
       </c>
       <c r="F26">
-        <v>129.2689104737093</v>
+        <v>134.6551150767805</v>
       </c>
       <c r="G26">
         <v>52.7</v>
@@ -3419,28 +3419,28 @@
         <v>77.741</v>
       </c>
       <c r="M26">
-        <v>6.696129562538141</v>
+        <v>6.975134960977232</v>
       </c>
       <c r="N26">
-        <v>71.04487043746185</v>
+        <v>70.76586503902277</v>
       </c>
       <c r="O26">
-        <v>21.31346113123855</v>
+        <v>21.22975951170683</v>
       </c>
       <c r="P26">
-        <v>49.7314093062233</v>
+        <v>49.53610552731594</v>
       </c>
       <c r="Q26">
-        <v>73.0314093062233</v>
+        <v>72.83610552731594</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1031112829866864</v>
+        <v>0.103687689568449</v>
       </c>
       <c r="T26">
-        <v>1.323586212163658</v>
+        <v>1.336898142458407</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.60984106922396</v>
+        <v>11.145447426455</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08683076717633678</v>
+        <v>0.08659455928279189</v>
       </c>
       <c r="C27">
-        <v>411.1832053482315</v>
+        <v>406.5854920394244</v>
       </c>
       <c r="D27">
-        <v>493.1383204250121</v>
+        <v>493.9268117192761</v>
       </c>
       <c r="E27">
-        <v>40.33465476965841</v>
+        <v>45.72085937272965</v>
       </c>
       <c r="F27">
-        <v>134.6551150767805</v>
+        <v>140.0413196798518</v>
       </c>
       <c r="G27">
         <v>52.7</v>
@@ -3501,28 +3501,28 @@
         <v>77.741</v>
       </c>
       <c r="M27">
-        <v>6.975134960977232</v>
+        <v>7.254140359416321</v>
       </c>
       <c r="N27">
-        <v>70.76586503902277</v>
+        <v>70.48685964058367</v>
       </c>
       <c r="O27">
-        <v>21.22975951170683</v>
+        <v>21.1460578921751</v>
       </c>
       <c r="P27">
-        <v>49.53610552731594</v>
+        <v>49.34080174840857</v>
       </c>
       <c r="Q27">
-        <v>72.83610552731594</v>
+        <v>72.64080174840858</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.103687689568449</v>
+        <v>0.1042796747064755</v>
       </c>
       <c r="T27">
-        <v>1.336898142458407</v>
+        <v>1.350569854653015</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.145447426455</v>
+        <v>10.71677637159135</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08659455928279189</v>
+        <v>0.08635835138924702</v>
       </c>
       <c r="C28">
-        <v>406.5854920394244</v>
+        <v>401.9903042459492</v>
       </c>
       <c r="D28">
-        <v>493.9268117192761</v>
+        <v>494.7178285288722</v>
       </c>
       <c r="E28">
-        <v>45.72085937272965</v>
+        <v>51.10706397580086</v>
       </c>
       <c r="F28">
-        <v>140.0413196798518</v>
+        <v>145.427524282923</v>
       </c>
       <c r="G28">
         <v>52.7</v>
@@ -3583,28 +3583,28 @@
         <v>77.741</v>
       </c>
       <c r="M28">
-        <v>7.254140359416321</v>
+        <v>7.53314575785541</v>
       </c>
       <c r="N28">
-        <v>70.48685964058367</v>
+        <v>70.20785424214459</v>
       </c>
       <c r="O28">
-        <v>21.1460578921751</v>
+        <v>21.06235627264338</v>
       </c>
       <c r="P28">
-        <v>49.34080174840857</v>
+        <v>49.14549796950121</v>
       </c>
       <c r="Q28">
-        <v>72.64080174840858</v>
+        <v>72.44549796950122</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1042796747064755</v>
+        <v>0.1048878786154069</v>
       </c>
       <c r="T28">
-        <v>1.350569854653015</v>
+        <v>1.364616134305009</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.71677637159135</v>
+        <v>10.31985872819908</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08635835138924702</v>
+        <v>0.08612214349570214</v>
       </c>
       <c r="C29">
-        <v>401.9903042459492</v>
+        <v>397.3976541210008</v>
       </c>
       <c r="D29">
-        <v>494.7178285288722</v>
+        <v>495.5113830069949</v>
       </c>
       <c r="E29">
-        <v>51.10706397580086</v>
+        <v>56.49326857887209</v>
       </c>
       <c r="F29">
-        <v>145.427524282923</v>
+        <v>150.8137288859942</v>
       </c>
       <c r="G29">
         <v>52.7</v>
@@ -3665,28 +3665,28 @@
         <v>77.741</v>
       </c>
       <c r="M29">
-        <v>7.53314575785541</v>
+        <v>7.8121511562945</v>
       </c>
       <c r="N29">
-        <v>70.20785424214459</v>
+        <v>69.9288488437055</v>
       </c>
       <c r="O29">
-        <v>21.06235627264338</v>
+        <v>20.97865465311165</v>
       </c>
       <c r="P29">
-        <v>49.14549796950121</v>
+        <v>48.95019419059385</v>
       </c>
       <c r="Q29">
-        <v>72.44549796950122</v>
+        <v>72.25019419059385</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1048878786154069</v>
+        <v>0.1055129770773641</v>
       </c>
       <c r="T29">
-        <v>1.364616134305009</v>
+        <v>1.379052588391781</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.31985872819908</v>
+        <v>9.951292345049108</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08612214349570214</v>
+        <v>0.08623103560215727</v>
       </c>
       <c r="C30">
-        <v>397.3976541210008</v>
+        <v>391.6453039482137</v>
       </c>
       <c r="D30">
-        <v>495.5113830069949</v>
+        <v>495.1452374372791</v>
       </c>
       <c r="E30">
-        <v>56.49326857887209</v>
+        <v>61.87947318194333</v>
       </c>
       <c r="F30">
-        <v>150.8137288859942</v>
+        <v>156.1999334890654</v>
       </c>
       <c r="G30">
         <v>52.7</v>
@@ -3747,45 +3747,45 @@
         <v>77.741</v>
       </c>
       <c r="M30">
-        <v>7.8121511562945</v>
+        <v>8.356696441665001</v>
       </c>
       <c r="N30">
-        <v>69.9288488437055</v>
+        <v>69.38430355833501</v>
       </c>
       <c r="O30">
-        <v>20.97865465311165</v>
+        <v>20.8152910675005</v>
       </c>
       <c r="P30">
-        <v>48.95019419059385</v>
+        <v>48.56901249083451</v>
       </c>
       <c r="Q30">
-        <v>72.25019419059385</v>
+        <v>71.86901249083451</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1055129770773641</v>
+        <v>0.1061556839467004</v>
       </c>
       <c r="T30">
-        <v>1.379052588391781</v>
+        <v>1.393895703157053</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>9.951292345049108</v>
+        <v>9.302838812284389</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08623103560215727</v>
+        <v>0.08600672770861238</v>
       </c>
       <c r="C31">
-        <v>391.6453039482137</v>
+        <v>387.0139177186372</v>
       </c>
       <c r="D31">
-        <v>495.1452374372791</v>
+        <v>495.9000558107738</v>
       </c>
       <c r="E31">
-        <v>61.8794731819433</v>
+        <v>67.2656777850145</v>
       </c>
       <c r="F31">
-        <v>156.1999334890654</v>
+        <v>161.5861380921366</v>
       </c>
       <c r="G31">
         <v>52.7</v>
@@ -3829,28 +3829,28 @@
         <v>77.741</v>
       </c>
       <c r="M31">
-        <v>8.356696441664999</v>
+        <v>8.644858387929309</v>
       </c>
       <c r="N31">
-        <v>69.38430355833501</v>
+        <v>69.0961416120707</v>
       </c>
       <c r="O31">
-        <v>20.8152910675005</v>
+        <v>20.72884248362121</v>
       </c>
       <c r="P31">
-        <v>48.56901249083451</v>
+        <v>48.36729912844949</v>
       </c>
       <c r="Q31">
-        <v>71.86901249083451</v>
+        <v>71.66729912844949</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1061556839467004</v>
+        <v>0.1068167538694463</v>
       </c>
       <c r="T31">
-        <v>1.393895703157053</v>
+        <v>1.409162906915619</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.30283881228439</v>
+        <v>8.992744185208243</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08600672770861238</v>
+        <v>0.0857824198150675</v>
       </c>
       <c r="C32">
-        <v>387.0139177186372</v>
+        <v>382.3848363507852</v>
       </c>
       <c r="D32">
-        <v>495.9000558107738</v>
+        <v>496.6571790459931</v>
       </c>
       <c r="E32">
-        <v>67.2656777850145</v>
+        <v>72.65188238808574</v>
       </c>
       <c r="F32">
-        <v>161.5861380921366</v>
+        <v>166.9723426952079</v>
       </c>
       <c r="G32">
         <v>52.7</v>
@@ -3911,28 +3911,28 @@
         <v>77.741</v>
       </c>
       <c r="M32">
-        <v>8.644858387929309</v>
+        <v>8.933020334193619</v>
       </c>
       <c r="N32">
-        <v>69.0961416120707</v>
+        <v>68.80797966580639</v>
       </c>
       <c r="O32">
-        <v>20.72884248362121</v>
+        <v>20.64239389974191</v>
       </c>
       <c r="P32">
-        <v>48.36729912844949</v>
+        <v>48.16558576606447</v>
       </c>
       <c r="Q32">
-        <v>71.66729912844949</v>
+        <v>71.46558576606446</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1068167538694463</v>
+        <v>0.1074969852392283</v>
       </c>
       <c r="T32">
-        <v>1.409162906915619</v>
+        <v>1.42487263831936</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.992744185208243</v>
+        <v>8.702655663104752</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0857824198150675</v>
+        <v>0.08555811192152263</v>
       </c>
       <c r="C33">
-        <v>382.3848363507852</v>
+        <v>377.7580704177526</v>
       </c>
       <c r="D33">
-        <v>496.6571790459931</v>
+        <v>497.4166177160317</v>
       </c>
       <c r="E33">
-        <v>72.65188238808574</v>
+        <v>78.03808699115697</v>
       </c>
       <c r="F33">
-        <v>166.9723426952079</v>
+        <v>172.3585472982791</v>
       </c>
       <c r="G33">
         <v>52.7</v>
@@ -3993,28 +3993,28 @@
         <v>77.741</v>
       </c>
       <c r="M33">
-        <v>8.933020334193619</v>
+        <v>9.221182280457931</v>
       </c>
       <c r="N33">
-        <v>68.80797966580639</v>
+        <v>68.51981771954206</v>
       </c>
       <c r="O33">
-        <v>20.64239389974191</v>
+        <v>20.55594531586262</v>
       </c>
       <c r="P33">
-        <v>48.16558576606447</v>
+        <v>47.96387240367945</v>
       </c>
       <c r="Q33">
-        <v>71.46558576606446</v>
+        <v>71.26387240367944</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1074969852392283</v>
+        <v>0.1081972234140039</v>
       </c>
       <c r="T33">
-        <v>1.42487263831936</v>
+        <v>1.441044420646741</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.702655663104752</v>
+        <v>8.430697673632725</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08555811192152263</v>
+        <v>0.08533380402797776</v>
       </c>
       <c r="C34">
-        <v>377.7580704177526</v>
+        <v>373.1336305574022</v>
       </c>
       <c r="D34">
-        <v>497.4166177160317</v>
+        <v>498.1783824587525</v>
       </c>
       <c r="E34">
-        <v>78.03808699115697</v>
+        <v>83.42429159422818</v>
       </c>
       <c r="F34">
-        <v>172.3585472982791</v>
+        <v>177.7447519013503</v>
       </c>
       <c r="G34">
         <v>52.7</v>
@@ -4075,28 +4075,28 @@
         <v>77.741</v>
       </c>
       <c r="M34">
-        <v>9.221182280457931</v>
+        <v>9.509344226722241</v>
       </c>
       <c r="N34">
-        <v>68.51981771954206</v>
+        <v>68.23165577327777</v>
       </c>
       <c r="O34">
-        <v>20.55594531586262</v>
+        <v>20.46949673198333</v>
       </c>
       <c r="P34">
-        <v>47.96387240367945</v>
+        <v>47.76215904129444</v>
       </c>
       <c r="Q34">
-        <v>71.26387240367944</v>
+        <v>71.06215904129444</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1081972234140039</v>
+        <v>0.1089183642208623</v>
       </c>
       <c r="T34">
-        <v>1.441044420646741</v>
+        <v>1.457698942745089</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.430697673632725</v>
+        <v>8.175221986552948</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08533380402797776</v>
+        <v>0.08510949613443287</v>
       </c>
       <c r="C35">
-        <v>373.1336305574022</v>
+        <v>368.5115274728623</v>
       </c>
       <c r="D35">
-        <v>498.1783824587525</v>
+        <v>498.9424839772838</v>
       </c>
       <c r="E35">
-        <v>83.42429159422818</v>
+        <v>88.81049619729941</v>
       </c>
       <c r="F35">
-        <v>177.7447519013503</v>
+        <v>183.1309565044215</v>
       </c>
       <c r="G35">
         <v>52.7</v>
@@ -4157,28 +4157,28 @@
         <v>77.741</v>
       </c>
       <c r="M35">
-        <v>9.509344226722241</v>
+        <v>9.797506172986552</v>
       </c>
       <c r="N35">
-        <v>68.23165577327777</v>
+        <v>67.94349382701344</v>
       </c>
       <c r="O35">
-        <v>20.46949673198333</v>
+        <v>20.38304814810403</v>
       </c>
       <c r="P35">
-        <v>47.76215904129444</v>
+        <v>47.56044567890941</v>
       </c>
       <c r="Q35">
-        <v>71.06215904129444</v>
+        <v>70.86044567890941</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1089183642208623</v>
+        <v>0.1096613577794438</v>
       </c>
       <c r="T35">
-        <v>1.457698942745089</v>
+        <v>1.474858147331265</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.175221986552948</v>
+        <v>7.934774281066095</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08510949613443287</v>
+        <v>0.084885188240888</v>
       </c>
       <c r="C36">
-        <v>368.5115274728623</v>
+        <v>363.8917719330269</v>
       </c>
       <c r="D36">
-        <v>498.9424839772838</v>
+        <v>499.7089330405196</v>
       </c>
       <c r="E36">
-        <v>88.81049619729941</v>
+        <v>94.19670080037065</v>
       </c>
       <c r="F36">
-        <v>183.1309565044215</v>
+        <v>188.5171611074928</v>
       </c>
       <c r="G36">
         <v>52.7</v>
@@ -4239,28 +4239,28 @@
         <v>77.741</v>
       </c>
       <c r="M36">
-        <v>9.797506172986552</v>
+        <v>10.08566811925086</v>
       </c>
       <c r="N36">
-        <v>67.94349382701344</v>
+        <v>67.65533188074913</v>
       </c>
       <c r="O36">
-        <v>20.38304814810403</v>
+        <v>20.29659956422474</v>
       </c>
       <c r="P36">
-        <v>47.56044567890941</v>
+        <v>47.3587323165244</v>
       </c>
       <c r="Q36">
-        <v>70.86044567890941</v>
+        <v>70.65873231652439</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1096613577794438</v>
+        <v>0.1104272126782893</v>
       </c>
       <c r="T36">
-        <v>1.474858147331265</v>
+        <v>1.49254532744317</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.934774281066095</v>
+        <v>7.708066444464206</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.084885188240888</v>
+        <v>0.08486248034734313</v>
       </c>
       <c r="C37">
-        <v>363.8917719330269</v>
+        <v>358.5832903669515</v>
       </c>
       <c r="D37">
-        <v>499.7089330405196</v>
+        <v>499.7866560775155</v>
       </c>
       <c r="E37">
-        <v>94.19670080037065</v>
+        <v>99.58290540344188</v>
       </c>
       <c r="F37">
-        <v>188.5171611074928</v>
+        <v>193.903365710564</v>
       </c>
       <c r="G37">
         <v>52.7</v>
@@ -4321,45 +4321,45 @@
         <v>77.741</v>
       </c>
       <c r="M37">
-        <v>10.08566811925086</v>
+        <v>10.52895275808363</v>
       </c>
       <c r="N37">
-        <v>67.65533188074913</v>
+        <v>67.21204724191637</v>
       </c>
       <c r="O37">
-        <v>20.29659956422474</v>
+        <v>20.16361417257491</v>
       </c>
       <c r="P37">
-        <v>47.3587323165244</v>
+        <v>47.04843306934146</v>
       </c>
       <c r="Q37">
-        <v>70.65873231652439</v>
+        <v>70.34843306934145</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1104272126782893</v>
+        <v>0.1112170005427237</v>
       </c>
       <c r="T37">
-        <v>1.49254532744317</v>
+        <v>1.510785231933572</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.708066444464206</v>
+        <v>7.383545333159005</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08486248034734314</v>
+        <v>0.08464377245379825</v>
       </c>
       <c r="C38">
-        <v>358.5832903669515</v>
+        <v>353.9469039805966</v>
       </c>
       <c r="D38">
-        <v>499.7866560775155</v>
+        <v>500.5364742942318</v>
       </c>
       <c r="E38">
-        <v>99.58290540344183</v>
+        <v>104.9691100065131</v>
       </c>
       <c r="F38">
-        <v>193.9033657105639</v>
+        <v>199.2895703136352</v>
       </c>
       <c r="G38">
         <v>52.7</v>
@@ -4403,28 +4403,28 @@
         <v>77.741</v>
       </c>
       <c r="M38">
-        <v>10.52895275808362</v>
+        <v>10.82142366803039</v>
       </c>
       <c r="N38">
-        <v>67.21204724191638</v>
+        <v>66.91957633196961</v>
       </c>
       <c r="O38">
-        <v>20.16361417257491</v>
+        <v>20.07587289959088</v>
       </c>
       <c r="P38">
-        <v>47.04843306934147</v>
+        <v>46.84370343237873</v>
       </c>
       <c r="Q38">
-        <v>70.34843306934147</v>
+        <v>70.14370343237873</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1112170005427237</v>
+        <v>0.112031861037775</v>
       </c>
       <c r="T38">
-        <v>1.510785231933572</v>
+        <v>1.52960418101097</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.383545333159009</v>
+        <v>7.18399005388444</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08464377245379825</v>
+        <v>0.08442506456025337</v>
       </c>
       <c r="C39">
-        <v>353.9469039805966</v>
+        <v>349.3127708441643</v>
       </c>
       <c r="D39">
-        <v>500.5364742942318</v>
+        <v>501.2885457608707</v>
       </c>
       <c r="E39">
-        <v>104.9691100065131</v>
+        <v>110.3553146095843</v>
       </c>
       <c r="F39">
-        <v>199.2895703136352</v>
+        <v>204.6757749167064</v>
       </c>
       <c r="G39">
         <v>52.7</v>
@@ -4485,28 +4485,28 @@
         <v>77.741</v>
       </c>
       <c r="M39">
-        <v>10.82142366803039</v>
+        <v>11.11389457797716</v>
       </c>
       <c r="N39">
-        <v>66.91957633196961</v>
+        <v>66.62710542202284</v>
       </c>
       <c r="O39">
-        <v>20.07587289959088</v>
+        <v>19.98813162660685</v>
       </c>
       <c r="P39">
-        <v>46.84370343237873</v>
+        <v>46.63897379541599</v>
       </c>
       <c r="Q39">
-        <v>70.14370343237873</v>
+        <v>69.93897379541599</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.112031861037775</v>
+        <v>0.1128730073552474</v>
       </c>
       <c r="T39">
-        <v>1.52960418101097</v>
+        <v>1.549030192961834</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.18399005388444</v>
+        <v>6.994937684045375</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08442506456025337</v>
+        <v>0.0842063566667085</v>
       </c>
       <c r="C40">
-        <v>349.3127708441643</v>
+        <v>344.6809011296704</v>
       </c>
       <c r="D40">
-        <v>501.2885457608707</v>
+        <v>502.042880649448</v>
       </c>
       <c r="E40">
-        <v>110.3553146095843</v>
+        <v>115.7415192126555</v>
       </c>
       <c r="F40">
-        <v>204.6757749167064</v>
+        <v>210.0619795197777</v>
       </c>
       <c r="G40">
         <v>52.7</v>
@@ -4567,28 +4567,28 @@
         <v>77.741</v>
       </c>
       <c r="M40">
-        <v>11.11389457797716</v>
+        <v>11.40636548792393</v>
       </c>
       <c r="N40">
-        <v>66.62710542202284</v>
+        <v>66.33463451207608</v>
       </c>
       <c r="O40">
-        <v>19.98813162660685</v>
+        <v>19.90039035362282</v>
       </c>
       <c r="P40">
-        <v>46.63897379541599</v>
+        <v>46.43424415845325</v>
       </c>
       <c r="Q40">
-        <v>69.93897379541599</v>
+        <v>69.73424415845325</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1128730073552474</v>
+        <v>0.1137417322405057</v>
       </c>
       <c r="T40">
-        <v>1.549030192961834</v>
+        <v>1.569093123337316</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.994937684045375</v>
+        <v>6.815580307531391</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0842063566667085</v>
+        <v>0.08398764877316363</v>
       </c>
       <c r="C41">
-        <v>344.6809011296704</v>
+        <v>340.0513050704502</v>
       </c>
       <c r="D41">
-        <v>502.042880649448</v>
+        <v>502.799489193299</v>
       </c>
       <c r="E41">
-        <v>115.7415192126555</v>
+        <v>121.1277238157267</v>
       </c>
       <c r="F41">
-        <v>210.0619795197777</v>
+        <v>215.4481841228489</v>
       </c>
       <c r="G41">
         <v>52.7</v>
@@ -4649,28 +4649,28 @@
         <v>77.741</v>
       </c>
       <c r="M41">
-        <v>11.40636548792393</v>
+        <v>11.69883639787069</v>
       </c>
       <c r="N41">
-        <v>66.33463451207608</v>
+        <v>66.04216360212931</v>
       </c>
       <c r="O41">
-        <v>19.90039035362282</v>
+        <v>19.81264908063879</v>
       </c>
       <c r="P41">
-        <v>46.43424415845325</v>
+        <v>46.22951452149051</v>
       </c>
       <c r="Q41">
-        <v>69.73424415845325</v>
+        <v>69.52951452149051</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1137417322405057</v>
+        <v>0.1146394146219394</v>
       </c>
       <c r="T41">
-        <v>1.569093123337316</v>
+        <v>1.589824818058647</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.815580307531391</v>
+        <v>6.645190799843107</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08398764877316363</v>
+        <v>0.08376894087961875</v>
       </c>
       <c r="C42">
-        <v>340.0513050704502</v>
+        <v>335.4239929616211</v>
       </c>
       <c r="D42">
-        <v>502.799489193299</v>
+        <v>503.5583816875413</v>
       </c>
       <c r="E42">
-        <v>121.1277238157267</v>
+        <v>126.513928418798</v>
       </c>
       <c r="F42">
-        <v>215.4481841228489</v>
+        <v>220.8343887259201</v>
       </c>
       <c r="G42">
         <v>52.7</v>
@@ -4731,28 +4731,28 @@
         <v>77.741</v>
       </c>
       <c r="M42">
-        <v>11.69883639787069</v>
+        <v>11.99130730781746</v>
       </c>
       <c r="N42">
-        <v>66.04216360212931</v>
+        <v>65.74969269218253</v>
       </c>
       <c r="O42">
-        <v>19.81264908063879</v>
+        <v>19.72490780765476</v>
       </c>
       <c r="P42">
-        <v>46.22951452149051</v>
+        <v>46.02478488452778</v>
       </c>
       <c r="Q42">
-        <v>69.52951452149051</v>
+        <v>69.32478488452777</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1146394146219394</v>
+        <v>0.1155675269146081</v>
       </c>
       <c r="T42">
-        <v>1.589824818058647</v>
+        <v>1.611259282092565</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.645190799843107</v>
+        <v>6.483112975456689</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08376894087961875</v>
+        <v>0.08355023298607388</v>
       </c>
       <c r="C43">
-        <v>335.4239929616211</v>
+        <v>330.7989751605497</v>
       </c>
       <c r="D43">
-        <v>503.5583816875413</v>
+        <v>504.319568489541</v>
       </c>
       <c r="E43">
-        <v>126.513928418798</v>
+        <v>131.9001330218692</v>
       </c>
       <c r="F43">
-        <v>220.8343887259201</v>
+        <v>226.2205933289913</v>
       </c>
       <c r="G43">
         <v>52.7</v>
@@ -4813,28 +4813,28 @@
         <v>77.741</v>
       </c>
       <c r="M43">
-        <v>11.99130730781746</v>
+        <v>12.28377821776423</v>
       </c>
       <c r="N43">
-        <v>65.74969269218253</v>
+        <v>65.45722178223576</v>
       </c>
       <c r="O43">
-        <v>19.72490780765476</v>
+        <v>19.63716653467073</v>
       </c>
       <c r="P43">
-        <v>46.02478488452778</v>
+        <v>45.82005524756504</v>
       </c>
       <c r="Q43">
-        <v>69.32478488452777</v>
+        <v>69.12005524756503</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1155675269146081</v>
+        <v>0.1165276430794377</v>
       </c>
       <c r="T43">
-        <v>1.611259282092565</v>
+        <v>1.633432865575929</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.483112975456689</v>
+        <v>6.328753142707719</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08355023298607388</v>
+        <v>0.083331525092529</v>
       </c>
       <c r="C44">
-        <v>330.7989751605497</v>
+        <v>326.1762620873227</v>
       </c>
       <c r="D44">
-        <v>504.319568489541</v>
+        <v>505.0830600193851</v>
       </c>
       <c r="E44">
-        <v>131.9001330218692</v>
+        <v>137.2863376249404</v>
       </c>
       <c r="F44">
-        <v>226.2205933289913</v>
+        <v>231.6067979320625</v>
       </c>
       <c r="G44">
         <v>52.7</v>
@@ -4895,28 +4895,28 @@
         <v>77.741</v>
       </c>
       <c r="M44">
-        <v>12.28377821776423</v>
+        <v>12.57624912771099</v>
       </c>
       <c r="N44">
-        <v>65.45722178223578</v>
+        <v>65.16475087228901</v>
       </c>
       <c r="O44">
-        <v>19.63716653467073</v>
+        <v>19.5494252616867</v>
       </c>
       <c r="P44">
-        <v>45.82005524756504</v>
+        <v>45.61532561060231</v>
       </c>
       <c r="Q44">
-        <v>69.12005524756505</v>
+        <v>68.91532561060231</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1165276430794377</v>
+        <v>0.1175214475307526</v>
       </c>
       <c r="T44">
-        <v>1.633432865575929</v>
+        <v>1.656384469532394</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.328753142707721</v>
+        <v>6.181572837063356</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.083331525092529</v>
+        <v>0.08342081719898413</v>
       </c>
       <c r="C45">
-        <v>326.1762620873227</v>
+        <v>320.4780669126372</v>
       </c>
       <c r="D45">
-        <v>505.0830600193851</v>
+        <v>504.771069447771</v>
       </c>
       <c r="E45">
-        <v>137.2863376249404</v>
+        <v>142.6725422280116</v>
       </c>
       <c r="F45">
-        <v>231.6067979320625</v>
+        <v>236.9930025351337</v>
       </c>
       <c r="G45">
         <v>52.7</v>
@@ -4977,45 +4977,45 @@
         <v>77.741</v>
       </c>
       <c r="M45">
-        <v>12.57624912771099</v>
+        <v>13.1057130401929</v>
       </c>
       <c r="N45">
-        <v>65.16475087228901</v>
+        <v>64.6352869598071</v>
       </c>
       <c r="O45">
-        <v>19.5494252616867</v>
+        <v>19.39058608794213</v>
       </c>
       <c r="P45">
-        <v>45.61532561060231</v>
+        <v>45.24470087186498</v>
       </c>
       <c r="Q45">
-        <v>68.91532561060231</v>
+        <v>68.54470087186498</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1175214475307526</v>
+        <v>0.1185507449981859</v>
       </c>
       <c r="T45">
-        <v>1.656384469532394</v>
+        <v>1.68015577363016</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.181572837063356</v>
+        <v>5.93184054630085</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08342081719898413</v>
+        <v>0.08320910930543926</v>
       </c>
       <c r="C46">
-        <v>320.4780669126372</v>
+        <v>315.8322064017386</v>
       </c>
       <c r="D46">
-        <v>504.771069447771</v>
+        <v>505.5114135399435</v>
       </c>
       <c r="E46">
-        <v>142.6725422280116</v>
+        <v>148.0587468310829</v>
       </c>
       <c r="F46">
-        <v>236.9930025351337</v>
+        <v>242.379207138205</v>
       </c>
       <c r="G46">
         <v>52.7</v>
@@ -5059,28 +5059,28 @@
         <v>77.741</v>
       </c>
       <c r="M46">
-        <v>13.1057130401929</v>
+        <v>13.40357015474274</v>
       </c>
       <c r="N46">
-        <v>64.6352869598071</v>
+        <v>64.33742984525726</v>
       </c>
       <c r="O46">
-        <v>19.39058608794213</v>
+        <v>19.30122895357718</v>
       </c>
       <c r="P46">
-        <v>45.24470087186498</v>
+        <v>45.03620089168008</v>
       </c>
       <c r="Q46">
-        <v>68.54470087186498</v>
+        <v>68.33620089168008</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1185507449981859</v>
+        <v>0.119617471464435</v>
       </c>
       <c r="T46">
-        <v>1.68015577363016</v>
+        <v>1.704791488786028</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.93184054630085</v>
+        <v>5.800021867494164</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08320910930543926</v>
+        <v>0.08299740141189438</v>
       </c>
       <c r="C47">
-        <v>315.8322064017386</v>
+        <v>311.1885207954528</v>
       </c>
       <c r="D47">
-        <v>505.5114135399435</v>
+        <v>506.2539325367289</v>
       </c>
       <c r="E47">
-        <v>148.0587468310829</v>
+        <v>153.4449514341541</v>
       </c>
       <c r="F47">
-        <v>242.379207138205</v>
+        <v>247.7654117412762</v>
       </c>
       <c r="G47">
         <v>52.7</v>
@@ -5141,28 +5141,28 @@
         <v>77.741</v>
       </c>
       <c r="M47">
-        <v>13.40357015474274</v>
+        <v>13.70142726929257</v>
       </c>
       <c r="N47">
-        <v>64.33742984525726</v>
+        <v>64.03957273070742</v>
       </c>
       <c r="O47">
-        <v>19.30122895357718</v>
+        <v>19.21187181921222</v>
       </c>
       <c r="P47">
-        <v>45.03620089168008</v>
+        <v>44.8277009114952</v>
       </c>
       <c r="Q47">
-        <v>68.33620089168008</v>
+        <v>68.1277009114952</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.119617471464435</v>
+        <v>0.1207237063183229</v>
       </c>
       <c r="T47">
-        <v>1.704791488786028</v>
+        <v>1.730339637836557</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.800021867494164</v>
+        <v>5.673934435592117</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08299740141189438</v>
+        <v>0.0827856935183495</v>
       </c>
       <c r="C48">
-        <v>311.1885207954528</v>
+        <v>306.5470196916851</v>
       </c>
       <c r="D48">
-        <v>506.2539325367289</v>
+        <v>506.9986360360325</v>
       </c>
       <c r="E48">
-        <v>153.4449514341541</v>
+        <v>158.8311560372253</v>
       </c>
       <c r="F48">
-        <v>247.7654117412762</v>
+        <v>253.1516163443474</v>
       </c>
       <c r="G48">
         <v>52.7</v>
@@ -5223,28 +5223,28 @@
         <v>77.741</v>
       </c>
       <c r="M48">
-        <v>13.70142726929257</v>
+        <v>13.99928438384241</v>
       </c>
       <c r="N48">
-        <v>64.03957273070742</v>
+        <v>63.74171561615758</v>
       </c>
       <c r="O48">
-        <v>19.21187181921222</v>
+        <v>19.12251468484727</v>
       </c>
       <c r="P48">
-        <v>44.8277009114952</v>
+        <v>44.61920093131031</v>
       </c>
       <c r="Q48">
-        <v>68.1277009114952</v>
+        <v>67.91920093131031</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1207237063183229</v>
+        <v>0.1218716858836783</v>
       </c>
       <c r="T48">
-        <v>1.730339637836557</v>
+        <v>1.756851867983333</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.673934435592117</v>
+        <v>5.553212426324199</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0827856935183495</v>
+        <v>0.08257398562480464</v>
       </c>
       <c r="C49">
-        <v>306.5470196916851</v>
+        <v>301.9077127448981</v>
       </c>
       <c r="D49">
-        <v>506.9986360360325</v>
+        <v>507.7455336923167</v>
       </c>
       <c r="E49">
-        <v>158.8311560372253</v>
+        <v>164.2173606402965</v>
       </c>
       <c r="F49">
-        <v>253.1516163443474</v>
+        <v>258.5378209474187</v>
       </c>
       <c r="G49">
         <v>52.7</v>
@@ -5305,28 +5305,28 @@
         <v>77.741</v>
       </c>
       <c r="M49">
-        <v>13.99928438384241</v>
+        <v>14.29714149839225</v>
       </c>
       <c r="N49">
-        <v>63.74171561615758</v>
+        <v>63.44385850160775</v>
       </c>
       <c r="O49">
-        <v>19.12251468484727</v>
+        <v>19.03315755048233</v>
       </c>
       <c r="P49">
-        <v>44.61920093131031</v>
+        <v>44.41070095112542</v>
       </c>
       <c r="Q49">
-        <v>67.91920093131031</v>
+        <v>67.71070095112542</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1218716858836783</v>
+        <v>0.1230638185092397</v>
       </c>
       <c r="T49">
-        <v>1.756851867983333</v>
+        <v>1.7843837992896</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.553212426324199</v>
+        <v>5.437520500775778</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08257398562480464</v>
+        <v>0.08236227773125974</v>
       </c>
       <c r="C50">
-        <v>301.9077127448982</v>
+        <v>297.2706096665297</v>
       </c>
       <c r="D50">
-        <v>507.7455336923167</v>
+        <v>508.4946352170195</v>
       </c>
       <c r="E50">
-        <v>164.2173606402965</v>
+        <v>169.6035652433677</v>
       </c>
       <c r="F50">
-        <v>258.5378209474186</v>
+        <v>263.9240255504898</v>
       </c>
       <c r="G50">
         <v>52.7</v>
@@ -5387,28 +5387,28 @@
         <v>77.741</v>
       </c>
       <c r="M50">
-        <v>14.29714149839225</v>
+        <v>14.59499861294209</v>
       </c>
       <c r="N50">
-        <v>63.44385850160775</v>
+        <v>63.14600138705791</v>
       </c>
       <c r="O50">
-        <v>19.03315755048233</v>
+        <v>18.94380041611737</v>
       </c>
       <c r="P50">
-        <v>44.41070095112542</v>
+        <v>44.20220097094054</v>
       </c>
       <c r="Q50">
-        <v>67.71070095112542</v>
+        <v>67.50220097094054</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1230638185092397</v>
+        <v>0.1243027014338426</v>
       </c>
       <c r="T50">
-        <v>1.7843837992896</v>
+        <v>1.812995414176505</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.437520500775779</v>
+        <v>5.326550694637498</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08236227773125974</v>
+        <v>0.08215056983771486</v>
       </c>
       <c r="C51">
-        <v>297.2706096665297</v>
+        <v>292.6357202254125</v>
       </c>
       <c r="D51">
-        <v>508.4946352170195</v>
+        <v>509.2459503789735</v>
       </c>
       <c r="E51">
-        <v>169.6035652433677</v>
+        <v>174.9897698464389</v>
       </c>
       <c r="F51">
-        <v>263.9240255504898</v>
+        <v>269.3102301535611</v>
       </c>
       <c r="G51">
         <v>52.7</v>
@@ -5469,28 +5469,28 @@
         <v>77.741</v>
       </c>
       <c r="M51">
-        <v>14.59499861294209</v>
+        <v>14.89285572749193</v>
       </c>
       <c r="N51">
-        <v>63.14600138705791</v>
+        <v>62.84814427250807</v>
       </c>
       <c r="O51">
-        <v>18.94380041611737</v>
+        <v>18.85444328175242</v>
       </c>
       <c r="P51">
-        <v>44.20220097094054</v>
+        <v>43.99370099075566</v>
       </c>
       <c r="Q51">
-        <v>67.50220097094054</v>
+        <v>67.29370099075565</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1243027014338426</v>
+        <v>0.1255911396754297</v>
       </c>
       <c r="T51">
-        <v>1.812995414176505</v>
+        <v>1.842751493658886</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.326550694637498</v>
+        <v>5.220019680744748</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08215056983771486</v>
+        <v>0.08193886194416999</v>
       </c>
       <c r="C52">
-        <v>292.6357202254125</v>
+        <v>288.0030542482004</v>
       </c>
       <c r="D52">
-        <v>509.2459503789735</v>
+        <v>509.9994890048327</v>
       </c>
       <c r="E52">
-        <v>174.9897698464389</v>
+        <v>180.3759744495102</v>
       </c>
       <c r="F52">
-        <v>269.3102301535611</v>
+        <v>274.6964347566323</v>
       </c>
       <c r="G52">
         <v>52.7</v>
@@ -5551,28 +5551,28 @@
         <v>77.741</v>
       </c>
       <c r="M52">
-        <v>14.89285572749193</v>
+        <v>15.19071284204177</v>
       </c>
       <c r="N52">
-        <v>62.84814427250807</v>
+        <v>62.55028715795823</v>
       </c>
       <c r="O52">
-        <v>18.85444328175242</v>
+        <v>18.76508614738747</v>
       </c>
       <c r="P52">
-        <v>43.99370099075566</v>
+        <v>43.78520101057076</v>
       </c>
       <c r="Q52">
-        <v>67.29370099075565</v>
+        <v>67.08520101057076</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1255911396754297</v>
+        <v>0.126932167233</v>
       </c>
       <c r="T52">
-        <v>1.842751493658886</v>
+        <v>1.873722106997691</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.220019680744748</v>
+        <v>5.117666353671321</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08193886194416999</v>
+        <v>0.08172715405062511</v>
       </c>
       <c r="C53">
-        <v>288.0030542482004</v>
+        <v>283.3726216197957</v>
       </c>
       <c r="D53">
-        <v>509.9994890048327</v>
+        <v>510.7552609794993</v>
       </c>
       <c r="E53">
-        <v>180.3759744495102</v>
+        <v>185.7621790525814</v>
       </c>
       <c r="F53">
-        <v>274.6964347566323</v>
+        <v>280.0826393597035</v>
       </c>
       <c r="G53">
         <v>52.7</v>
@@ -5633,28 +5633,28 @@
         <v>77.741</v>
       </c>
       <c r="M53">
-        <v>15.19071284204177</v>
+        <v>15.48856995659161</v>
       </c>
       <c r="N53">
-        <v>62.55028715795823</v>
+        <v>62.2524300434084</v>
       </c>
       <c r="O53">
-        <v>18.76508614738747</v>
+        <v>18.67572901302252</v>
       </c>
       <c r="P53">
-        <v>43.78520101057076</v>
+        <v>43.57670103038588</v>
       </c>
       <c r="Q53">
-        <v>67.08520101057076</v>
+        <v>66.87670103038587</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.126932167233</v>
+        <v>0.1283290709388023</v>
       </c>
       <c r="T53">
-        <v>1.873722106997691</v>
+        <v>1.905983162558946</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.117666353671321</v>
+        <v>5.019249693023796</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08172715405062511</v>
+        <v>0.08151544615708023</v>
       </c>
       <c r="C54">
-        <v>283.3726216197957</v>
+        <v>278.7444322837816</v>
       </c>
       <c r="D54">
-        <v>510.7552609794993</v>
+        <v>511.5132762465564</v>
       </c>
       <c r="E54">
-        <v>185.7621790525814</v>
+        <v>191.1483836556527</v>
       </c>
       <c r="F54">
-        <v>280.0826393597035</v>
+        <v>285.4688439627748</v>
       </c>
       <c r="G54">
         <v>52.7</v>
@@ -5715,28 +5715,28 @@
         <v>77.741</v>
       </c>
       <c r="M54">
-        <v>15.48856995659161</v>
+        <v>15.78642707114144</v>
       </c>
       <c r="N54">
-        <v>62.2524300434084</v>
+        <v>61.95457292885855</v>
       </c>
       <c r="O54">
-        <v>18.67572901302252</v>
+        <v>18.58637187865757</v>
       </c>
       <c r="P54">
-        <v>43.57670103038588</v>
+        <v>43.36820105020099</v>
       </c>
       <c r="Q54">
-        <v>66.87670103038587</v>
+        <v>66.66820105020099</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1283290709388023</v>
+        <v>0.1297854173554899</v>
       </c>
       <c r="T54">
-        <v>1.905983162558946</v>
+        <v>1.939617028995148</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.019249693023796</v>
+        <v>4.92454686862712</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08151544615708023</v>
+        <v>0.08130373826353536</v>
       </c>
       <c r="C55">
-        <v>278.7444322837816</v>
+        <v>274.1184962428586</v>
       </c>
       <c r="D55">
-        <v>511.5132762465564</v>
+        <v>512.2735448087045</v>
       </c>
       <c r="E55">
-        <v>191.1483836556527</v>
+        <v>196.5345882587238</v>
       </c>
       <c r="F55">
-        <v>285.4688439627748</v>
+        <v>290.8550485658459</v>
       </c>
       <c r="G55">
         <v>52.7</v>
@@ -5797,28 +5797,28 @@
         <v>77.741</v>
       </c>
       <c r="M55">
-        <v>15.78642707114144</v>
+        <v>16.08428418569128</v>
       </c>
       <c r="N55">
-        <v>61.95457292885855</v>
+        <v>61.65671581430872</v>
       </c>
       <c r="O55">
-        <v>18.58637187865757</v>
+        <v>18.49701474429261</v>
       </c>
       <c r="P55">
-        <v>43.36820105020099</v>
+        <v>43.15970107001611</v>
       </c>
       <c r="Q55">
-        <v>66.66820105020099</v>
+        <v>66.45970107001611</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1297854173554899</v>
+        <v>0.1313050831815986</v>
       </c>
       <c r="T55">
-        <v>1.939617028995148</v>
+        <v>1.974713237450315</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.92454686862712</v>
+        <v>4.833351556245137</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08130373826353536</v>
+        <v>0.08109203036999049</v>
       </c>
       <c r="C56">
-        <v>274.1184962428586</v>
+        <v>269.4948235592839</v>
       </c>
       <c r="D56">
-        <v>512.2735448087045</v>
+        <v>513.036076728201</v>
       </c>
       <c r="E56">
-        <v>196.5345882587238</v>
+        <v>201.9207928617951</v>
       </c>
       <c r="F56">
-        <v>290.8550485658459</v>
+        <v>296.2412531689172</v>
       </c>
       <c r="G56">
         <v>52.7</v>
@@ -5879,28 +5879,28 @@
         <v>77.741</v>
       </c>
       <c r="M56">
-        <v>16.08428418569128</v>
+        <v>16.38214130024112</v>
       </c>
       <c r="N56">
-        <v>61.65671581430872</v>
+        <v>61.35885869975888</v>
       </c>
       <c r="O56">
-        <v>18.49701474429261</v>
+        <v>18.40765760992766</v>
       </c>
       <c r="P56">
-        <v>43.15970107001611</v>
+        <v>42.95120108983122</v>
       </c>
       <c r="Q56">
-        <v>66.45970107001611</v>
+        <v>66.25120108983121</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1313050831815986</v>
+        <v>0.13289228971109</v>
       </c>
       <c r="T56">
-        <v>1.974713237450315</v>
+        <v>2.011369277392379</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.833351556245137</v>
+        <v>4.74547243704068</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08109203036999049</v>
+        <v>0.08088032247644562</v>
       </c>
       <c r="C57">
-        <v>269.4948235592839</v>
+        <v>264.8734243553161</v>
       </c>
       <c r="D57">
-        <v>513.036076728201</v>
+        <v>513.8008821273045</v>
       </c>
       <c r="E57">
-        <v>201.9207928617951</v>
+        <v>207.3069974648663</v>
       </c>
       <c r="F57">
-        <v>296.2412531689172</v>
+        <v>301.6274577719884</v>
       </c>
       <c r="G57">
         <v>52.7</v>
@@ -5961,28 +5961,28 @@
         <v>77.741</v>
       </c>
       <c r="M57">
-        <v>16.38214130024112</v>
+        <v>16.67999841479096</v>
       </c>
       <c r="N57">
-        <v>61.35885869975888</v>
+        <v>61.06100158520904</v>
       </c>
       <c r="O57">
-        <v>18.40765760992766</v>
+        <v>18.31830047556271</v>
       </c>
       <c r="P57">
-        <v>42.95120108983122</v>
+        <v>42.74270110964633</v>
       </c>
       <c r="Q57">
-        <v>66.25120108983121</v>
+        <v>66.04270110964633</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.13289228971109</v>
+        <v>0.1345516419919219</v>
       </c>
       <c r="T57">
-        <v>2.011369277392379</v>
+        <v>2.049691500968173</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.74547243704068</v>
+        <v>4.660731857807811</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08088032247644562</v>
+        <v>0.08066861458290074</v>
       </c>
       <c r="C58">
-        <v>264.8734243553161</v>
+        <v>260.2543088136624</v>
       </c>
       <c r="D58">
-        <v>513.8008821273045</v>
+        <v>514.567971188722</v>
       </c>
       <c r="E58">
-        <v>207.3069974648663</v>
+        <v>212.6932020679375</v>
       </c>
       <c r="F58">
-        <v>301.6274577719884</v>
+        <v>307.0136623750597</v>
       </c>
       <c r="G58">
         <v>52.7</v>
@@ -6043,28 +6043,28 @@
         <v>77.741</v>
       </c>
       <c r="M58">
-        <v>16.67999841479096</v>
+        <v>16.9778555293408</v>
       </c>
       <c r="N58">
-        <v>61.06100158520904</v>
+        <v>60.7631444706592</v>
       </c>
       <c r="O58">
-        <v>18.31830047556271</v>
+        <v>18.22894334119776</v>
       </c>
       <c r="P58">
-        <v>42.74270110964633</v>
+        <v>42.53420112946144</v>
       </c>
       <c r="Q58">
-        <v>66.04270110964633</v>
+        <v>65.83420112946143</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1345516419919219</v>
+        <v>0.1362881734486064</v>
       </c>
       <c r="T58">
-        <v>2.049691500968173</v>
+        <v>2.089796153547492</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.660731857807811</v>
+        <v>4.578964632232234</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08066861458290074</v>
+        <v>0.08045690668935586</v>
       </c>
       <c r="C59">
-        <v>260.2543088136624</v>
+        <v>255.6374871779313</v>
       </c>
       <c r="D59">
-        <v>514.567971188722</v>
+        <v>515.3373541560621</v>
       </c>
       <c r="E59">
-        <v>212.6932020679375</v>
+        <v>218.0794066710088</v>
       </c>
       <c r="F59">
-        <v>307.0136623750597</v>
+        <v>312.3998669781309</v>
       </c>
       <c r="G59">
         <v>52.7</v>
@@ -6125,28 +6125,28 @@
         <v>77.741</v>
       </c>
       <c r="M59">
-        <v>16.9778555293408</v>
+        <v>17.27571264389064</v>
       </c>
       <c r="N59">
-        <v>60.7631444706592</v>
+        <v>60.46528735610936</v>
       </c>
       <c r="O59">
-        <v>18.22894334119776</v>
+        <v>18.13958620683281</v>
       </c>
       <c r="P59">
-        <v>42.53420112946144</v>
+        <v>42.32570114927655</v>
       </c>
       <c r="Q59">
-        <v>65.83420112946143</v>
+        <v>65.62570114927655</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1362881734486064</v>
+        <v>0.1381073968794187</v>
       </c>
       <c r="T59">
-        <v>2.089796153547492</v>
+        <v>2.131810551487731</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.578964632232234</v>
+        <v>4.500016966159264</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08045690668935586</v>
+        <v>0.08127769879581098</v>
       </c>
       <c r="C60">
-        <v>255.6374871779313</v>
+        <v>247.2811402043827</v>
       </c>
       <c r="D60">
-        <v>515.3373541560621</v>
+        <v>512.3672117855847</v>
       </c>
       <c r="E60">
-        <v>218.0794066710087</v>
+        <v>223.4656112740799</v>
       </c>
       <c r="F60">
-        <v>312.3998669781308</v>
+        <v>317.7860715812021</v>
       </c>
       <c r="G60">
         <v>52.7</v>
@@ -6207,45 +6207,45 @@
         <v>77.741</v>
       </c>
       <c r="M60">
-        <v>17.27571264389064</v>
+        <v>18.36803493739348</v>
       </c>
       <c r="N60">
-        <v>60.46528735610936</v>
+        <v>59.37296506260652</v>
       </c>
       <c r="O60">
-        <v>18.13958620683281</v>
+        <v>17.81188951878195</v>
       </c>
       <c r="P60">
-        <v>42.32570114927655</v>
+        <v>41.56107554382456</v>
       </c>
       <c r="Q60">
-        <v>65.62570114927655</v>
+        <v>64.86107554382457</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1381073968794187</v>
+        <v>0.1400153629166122</v>
       </c>
       <c r="T60">
-        <v>2.13181055148773</v>
+        <v>2.175874432254322</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.500016966159265</v>
+        <v>4.232407019312424</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08127769879581098</v>
+        <v>0.08108349090226612</v>
       </c>
       <c r="C61">
-        <v>247.2811402043827</v>
+        <v>242.5946057296998</v>
       </c>
       <c r="D61">
-        <v>512.3672117855847</v>
+        <v>513.066881913973</v>
       </c>
       <c r="E61">
-        <v>223.4656112740799</v>
+        <v>228.8518158771511</v>
       </c>
       <c r="F61">
-        <v>317.7860715812021</v>
+        <v>323.1722761842732</v>
       </c>
       <c r="G61">
         <v>52.7</v>
@@ -6289,28 +6289,28 @@
         <v>77.741</v>
       </c>
       <c r="M61">
-        <v>18.36803493739348</v>
+        <v>18.679357563451</v>
       </c>
       <c r="N61">
-        <v>59.37296506260652</v>
+        <v>59.06164243654901</v>
       </c>
       <c r="O61">
-        <v>17.81188951878195</v>
+        <v>17.7184927309647</v>
       </c>
       <c r="P61">
-        <v>41.56107554382456</v>
+        <v>41.34314970558431</v>
       </c>
       <c r="Q61">
-        <v>64.86107554382457</v>
+        <v>64.64314970558431</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1400153629166122</v>
+        <v>0.1420187272556653</v>
       </c>
       <c r="T61">
-        <v>2.175874432254322</v>
+        <v>2.222141507059245</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.232407019312424</v>
+        <v>4.161866902323884</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08108349090226612</v>
+        <v>0.08088928300872124</v>
       </c>
       <c r="C62">
-        <v>242.5946057296998</v>
+        <v>237.9099847564557</v>
       </c>
       <c r="D62">
-        <v>513.066881913973</v>
+        <v>513.7684655438002</v>
       </c>
       <c r="E62">
-        <v>228.8518158771511</v>
+        <v>234.2380204802224</v>
       </c>
       <c r="F62">
-        <v>323.1722761842732</v>
+        <v>328.5584807873445</v>
       </c>
       <c r="G62">
         <v>52.7</v>
@@ -6371,28 +6371,28 @@
         <v>77.741</v>
       </c>
       <c r="M62">
-        <v>18.679357563451</v>
+        <v>18.99068018950851</v>
       </c>
       <c r="N62">
-        <v>59.06164243654901</v>
+        <v>58.75031981049149</v>
       </c>
       <c r="O62">
-        <v>17.7184927309647</v>
+        <v>17.62509594314745</v>
       </c>
       <c r="P62">
-        <v>41.34314970558431</v>
+        <v>41.12522386734405</v>
       </c>
       <c r="Q62">
-        <v>64.64314970558431</v>
+        <v>64.42522386734404</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1420187272556653</v>
+        <v>0.1441248282274903</v>
       </c>
       <c r="T62">
-        <v>2.222141507059245</v>
+        <v>2.270781252366983</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.161866902323884</v>
+        <v>4.093639576056279</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08088928300872124</v>
+        <v>0.08069507511517636</v>
       </c>
       <c r="C63">
-        <v>237.9099847564557</v>
+        <v>233.2272851451434</v>
       </c>
       <c r="D63">
-        <v>513.7684655438002</v>
+        <v>514.4719705355591</v>
       </c>
       <c r="E63">
-        <v>234.2380204802224</v>
+        <v>239.6242250832936</v>
       </c>
       <c r="F63">
-        <v>328.5584807873445</v>
+        <v>333.9446853904157</v>
       </c>
       <c r="G63">
         <v>52.7</v>
@@ -6453,28 +6453,28 @@
         <v>77.741</v>
       </c>
       <c r="M63">
-        <v>18.99068018950851</v>
+        <v>19.30200281556603</v>
       </c>
       <c r="N63">
-        <v>58.75031981049149</v>
+        <v>58.43899718443397</v>
       </c>
       <c r="O63">
-        <v>17.62509594314745</v>
+        <v>17.53169915533019</v>
       </c>
       <c r="P63">
-        <v>41.12522386734405</v>
+        <v>40.90729802910379</v>
       </c>
       <c r="Q63">
-        <v>64.42522386734404</v>
+        <v>64.20729802910378</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1441248282274903</v>
+        <v>0.1463417766188851</v>
       </c>
       <c r="T63">
-        <v>2.270781252366983</v>
+        <v>2.321980984269865</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.093639576056279</v>
+        <v>4.027613131281178</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08069507511517636</v>
+        <v>0.08204436722163148</v>
       </c>
       <c r="C64">
-        <v>233.2272851451434</v>
+        <v>222.9927921810822</v>
       </c>
       <c r="D64">
-        <v>514.4719705355591</v>
+        <v>509.6236821745692</v>
       </c>
       <c r="E64">
-        <v>239.6242250832936</v>
+        <v>245.0104296863648</v>
       </c>
       <c r="F64">
-        <v>333.9446853904157</v>
+        <v>339.3308899934869</v>
       </c>
       <c r="G64">
         <v>52.7</v>
@@ -6535,45 +6535,45 @@
         <v>77.741</v>
       </c>
       <c r="M64">
-        <v>19.30200281556603</v>
+        <v>20.80098355660075</v>
       </c>
       <c r="N64">
-        <v>58.43899718443397</v>
+        <v>56.94001644339924</v>
       </c>
       <c r="O64">
-        <v>17.53169915533019</v>
+        <v>17.08200493301977</v>
       </c>
       <c r="P64">
-        <v>40.90729802910379</v>
+        <v>39.85801151037947</v>
       </c>
       <c r="Q64">
-        <v>64.20729802910378</v>
+        <v>63.15801151037947</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1463417766188851</v>
+        <v>0.1486785600584635</v>
       </c>
       <c r="T64">
-        <v>2.321980984269865</v>
+        <v>2.37594826924858</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.027613131281178</v>
+        <v>3.737371350179763</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08204436722163148</v>
+        <v>0.0818746593280866</v>
       </c>
       <c r="C65">
-        <v>222.9927921810822</v>
+        <v>218.2113537026443</v>
       </c>
       <c r="D65">
-        <v>509.6236821745692</v>
+        <v>510.2284482992025</v>
       </c>
       <c r="E65">
-        <v>245.0104296863648</v>
+        <v>250.3966342894361</v>
       </c>
       <c r="F65">
-        <v>339.3308899934869</v>
+        <v>344.7170945965582</v>
       </c>
       <c r="G65">
         <v>52.7</v>
@@ -6617,28 +6617,28 @@
         <v>77.741</v>
       </c>
       <c r="M65">
-        <v>20.80098355660075</v>
+        <v>21.13115789876902</v>
       </c>
       <c r="N65">
-        <v>56.94001644339924</v>
+        <v>56.60984210123098</v>
       </c>
       <c r="O65">
-        <v>17.08200493301977</v>
+        <v>16.98295263036929</v>
       </c>
       <c r="P65">
-        <v>39.85801151037947</v>
+        <v>39.62688947086168</v>
       </c>
       <c r="Q65">
-        <v>63.15801151037947</v>
+        <v>62.92688947086168</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1486785600584635</v>
+        <v>0.1511451648002406</v>
       </c>
       <c r="T65">
-        <v>2.37594826924858</v>
+        <v>2.432913736726111</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.737371350179763</v>
+        <v>3.678974922833204</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0818746593280866</v>
+        <v>0.08170495143454173</v>
       </c>
       <c r="C66">
-        <v>218.2113537026443</v>
+        <v>213.431352271255</v>
       </c>
       <c r="D66">
-        <v>510.2284482992025</v>
+        <v>510.8346514708845</v>
       </c>
       <c r="E66">
-        <v>250.3966342894361</v>
+        <v>255.7828388925073</v>
       </c>
       <c r="F66">
-        <v>344.7170945965582</v>
+        <v>350.1032991996294</v>
       </c>
       <c r="G66">
         <v>52.7</v>
@@ -6699,28 +6699,28 @@
         <v>77.741</v>
       </c>
       <c r="M66">
-        <v>21.13115789876902</v>
+        <v>21.46133224093728</v>
       </c>
       <c r="N66">
-        <v>56.60984210123098</v>
+        <v>56.27966775906272</v>
       </c>
       <c r="O66">
-        <v>16.98295263036929</v>
+        <v>16.88390032771882</v>
       </c>
       <c r="P66">
-        <v>39.62688947086168</v>
+        <v>39.3957674313439</v>
       </c>
       <c r="Q66">
-        <v>62.92688947086168</v>
+        <v>62.6957674313439</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1511451648002406</v>
+        <v>0.1537527183844049</v>
       </c>
       <c r="T66">
-        <v>2.432913736726111</v>
+        <v>2.493134373773787</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.678974922833204</v>
+        <v>3.62237530863577</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08170495143454173</v>
+        <v>0.08153524354099685</v>
       </c>
       <c r="C67">
-        <v>213.431352271255</v>
+        <v>208.6527930150804</v>
       </c>
       <c r="D67">
-        <v>510.8346514708845</v>
+        <v>511.442296817781</v>
       </c>
       <c r="E67">
-        <v>255.7828388925073</v>
+        <v>261.1690434955785</v>
       </c>
       <c r="F67">
-        <v>350.1032991996294</v>
+        <v>355.4895038027006</v>
       </c>
       <c r="G67">
         <v>52.7</v>
@@ -6781,28 +6781,28 @@
         <v>77.741</v>
       </c>
       <c r="M67">
-        <v>21.46133224093728</v>
+        <v>21.79150658310555</v>
       </c>
       <c r="N67">
-        <v>56.27966775906272</v>
+        <v>55.94949341689446</v>
       </c>
       <c r="O67">
-        <v>16.88390032771882</v>
+        <v>16.78484802506834</v>
       </c>
       <c r="P67">
-        <v>39.3957674313439</v>
+        <v>39.16464539182612</v>
       </c>
       <c r="Q67">
-        <v>62.6957674313439</v>
+        <v>62.46464539182612</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1537527183844049</v>
+        <v>0.1565136574735202</v>
       </c>
       <c r="T67">
-        <v>2.493134373773787</v>
+        <v>2.556897401236032</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.62237530863577</v>
+        <v>3.567490834262502</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08153524354099685</v>
+        <v>0.08136553564745198</v>
       </c>
       <c r="C68">
-        <v>208.6527930150804</v>
+        <v>203.8756810867154</v>
       </c>
       <c r="D68">
-        <v>511.442296817781</v>
+        <v>512.0513894924871</v>
       </c>
       <c r="E68">
-        <v>261.1690434955785</v>
+        <v>266.5552480986497</v>
       </c>
       <c r="F68">
-        <v>355.4895038027006</v>
+        <v>360.8757084057718</v>
       </c>
       <c r="G68">
         <v>52.7</v>
@@ -6863,28 +6863,28 @@
         <v>77.741</v>
       </c>
       <c r="M68">
-        <v>21.79150658310555</v>
+        <v>22.12168092527381</v>
       </c>
       <c r="N68">
-        <v>55.94949341689446</v>
+        <v>55.61931907472619</v>
       </c>
       <c r="O68">
-        <v>16.78484802506834</v>
+        <v>16.68579572241785</v>
       </c>
       <c r="P68">
-        <v>39.16464539182612</v>
+        <v>38.93352335230833</v>
       </c>
       <c r="Q68">
-        <v>62.46464539182612</v>
+        <v>62.23352335230832</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1565136574735202</v>
+        <v>0.1594419262044</v>
       </c>
       <c r="T68">
-        <v>2.556897401236032</v>
+        <v>2.62452485460508</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.567490834262502</v>
+        <v>3.514244702407837</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08136553564745198</v>
+        <v>0.0825286277539071</v>
       </c>
       <c r="C69">
-        <v>203.8756810867154</v>
+        <v>194.3439279181216</v>
       </c>
       <c r="D69">
-        <v>512.0513894924871</v>
+        <v>507.9058409269647</v>
       </c>
       <c r="E69">
-        <v>266.5552480986497</v>
+        <v>271.9414527017209</v>
       </c>
       <c r="F69">
-        <v>360.8757084057718</v>
+        <v>366.2619130088431</v>
       </c>
       <c r="G69">
         <v>52.7</v>
@@ -6945,45 +6945,45 @@
         <v>77.741</v>
       </c>
       <c r="M69">
-        <v>22.12168092527381</v>
+        <v>23.47738862386684</v>
       </c>
       <c r="N69">
-        <v>55.61931907472619</v>
+        <v>54.26361137613316</v>
       </c>
       <c r="O69">
-        <v>16.68579572241785</v>
+        <v>16.27908341283995</v>
       </c>
       <c r="P69">
-        <v>38.93352335230833</v>
+        <v>37.98452796329321</v>
       </c>
       <c r="Q69">
-        <v>62.23352335230832</v>
+        <v>61.28452796329321</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1594419262044</v>
+        <v>0.1625532117309597</v>
       </c>
       <c r="T69">
-        <v>2.62452485460508</v>
+        <v>2.696379023809694</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.514244702407837</v>
+        <v>3.311313760039283</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0825286277539071</v>
+        <v>0.08237851986036222</v>
       </c>
       <c r="C70">
-        <v>194.3439279181216</v>
+        <v>189.4889686162374</v>
       </c>
       <c r="D70">
-        <v>507.9058409269647</v>
+        <v>508.4370862281517</v>
       </c>
       <c r="E70">
-        <v>271.9414527017209</v>
+        <v>277.3276573047922</v>
       </c>
       <c r="F70">
-        <v>366.2619130088431</v>
+        <v>371.6481176119143</v>
       </c>
       <c r="G70">
         <v>52.7</v>
@@ -7027,28 +7027,28 @@
         <v>77.741</v>
       </c>
       <c r="M70">
-        <v>23.47738862386684</v>
+        <v>23.82264433892371</v>
       </c>
       <c r="N70">
-        <v>54.26361137613316</v>
+        <v>53.91835566107629</v>
       </c>
       <c r="O70">
-        <v>16.27908341283995</v>
+        <v>16.17550669832289</v>
       </c>
       <c r="P70">
-        <v>37.98452796329321</v>
+        <v>37.7428489627534</v>
       </c>
       <c r="Q70">
-        <v>61.28452796329321</v>
+        <v>61.0428489627534</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1625532117309597</v>
+        <v>0.1658652253560072</v>
       </c>
       <c r="T70">
-        <v>2.696379023809694</v>
+        <v>2.772868945866218</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.311313760039283</v>
+        <v>3.26332370554596</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08237851986036222</v>
+        <v>0.08222841196681735</v>
       </c>
       <c r="C71">
-        <v>189.4889686162374</v>
+        <v>184.6351217924806</v>
       </c>
       <c r="D71">
-        <v>508.4370862281517</v>
+        <v>508.9694440074662</v>
       </c>
       <c r="E71">
-        <v>277.3276573047922</v>
+        <v>282.7138619078634</v>
       </c>
       <c r="F71">
-        <v>371.6481176119143</v>
+        <v>377.0343222149855</v>
       </c>
       <c r="G71">
         <v>52.7</v>
@@ -7109,28 +7109,28 @@
         <v>77.741</v>
       </c>
       <c r="M71">
-        <v>23.82264433892371</v>
+        <v>24.16790005398057</v>
       </c>
       <c r="N71">
-        <v>53.91835566107629</v>
+        <v>53.57309994601943</v>
       </c>
       <c r="O71">
-        <v>16.17550669832289</v>
+        <v>16.07192998380583</v>
       </c>
       <c r="P71">
-        <v>37.7428489627534</v>
+        <v>37.50116996221359</v>
       </c>
       <c r="Q71">
-        <v>61.0428489627534</v>
+        <v>60.80116996221359</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1658652253560072</v>
+        <v>0.1693980398893912</v>
       </c>
       <c r="T71">
-        <v>2.772868945866218</v>
+        <v>2.854458196059843</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.26332370554596</v>
+        <v>3.216704795466732</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08222841196681735</v>
+        <v>0.08207830407327249</v>
       </c>
       <c r="C72">
-        <v>184.6351217924806</v>
+        <v>179.7823909449664</v>
       </c>
       <c r="D72">
-        <v>508.9694440074662</v>
+        <v>509.5029177630231</v>
       </c>
       <c r="E72">
-        <v>282.7138619078634</v>
+        <v>288.1000665109347</v>
       </c>
       <c r="F72">
-        <v>377.0343222149855</v>
+        <v>382.4205268180568</v>
       </c>
       <c r="G72">
         <v>52.7</v>
@@ -7191,28 +7191,28 @@
         <v>77.741</v>
       </c>
       <c r="M72">
-        <v>24.16790005398057</v>
+        <v>24.51315576903744</v>
       </c>
       <c r="N72">
-        <v>53.57309994601943</v>
+        <v>53.22784423096256</v>
       </c>
       <c r="O72">
-        <v>16.07192998380583</v>
+        <v>15.96835326928877</v>
       </c>
       <c r="P72">
-        <v>37.50116996221359</v>
+        <v>37.25949096167379</v>
       </c>
       <c r="Q72">
-        <v>60.80116996221359</v>
+        <v>60.55949096167379</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1693980398893912</v>
+        <v>0.1731744968043879</v>
       </c>
       <c r="T72">
-        <v>2.854458196059843</v>
+        <v>2.941674291094409</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.216704795466732</v>
+        <v>3.17139909412213</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08207830407327246</v>
+        <v>0.0819281961797276</v>
       </c>
       <c r="C73">
-        <v>179.7823909449666</v>
+        <v>174.9307795864912</v>
       </c>
       <c r="D73">
-        <v>509.5029177630232</v>
+        <v>510.0375110076191</v>
       </c>
       <c r="E73">
-        <v>288.1000665109346</v>
+        <v>293.4862711140058</v>
       </c>
       <c r="F73">
-        <v>382.4205268180567</v>
+        <v>387.8067314211279</v>
       </c>
       <c r="G73">
         <v>52.7</v>
@@ -7273,28 +7273,28 @@
         <v>77.741</v>
       </c>
       <c r="M73">
-        <v>24.51315576903744</v>
+        <v>24.8584114840943</v>
       </c>
       <c r="N73">
-        <v>53.22784423096256</v>
+        <v>52.8825885159057</v>
       </c>
       <c r="O73">
-        <v>15.96835326928877</v>
+        <v>15.86477655477171</v>
       </c>
       <c r="P73">
-        <v>37.25949096167379</v>
+        <v>37.01781196113399</v>
       </c>
       <c r="Q73">
-        <v>60.55949096167379</v>
+        <v>60.31781196113398</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1731744968043878</v>
+        <v>0.1772207006418843</v>
       </c>
       <c r="T73">
-        <v>2.941674291094408</v>
+        <v>3.035120107202871</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.17139909412213</v>
+        <v>3.127351884481545</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0819281961797276</v>
+        <v>0.08177808828618273</v>
       </c>
       <c r="C74">
-        <v>174.9307795864912</v>
+        <v>170.0802912446102</v>
       </c>
       <c r="D74">
-        <v>510.0375110076191</v>
+        <v>510.5732272688094</v>
       </c>
       <c r="E74">
-        <v>293.4862711140058</v>
+        <v>298.872475717077</v>
       </c>
       <c r="F74">
-        <v>387.8067314211279</v>
+        <v>393.1929360241991</v>
       </c>
       <c r="G74">
         <v>52.7</v>
@@ -7355,28 +7355,28 @@
         <v>77.741</v>
       </c>
       <c r="M74">
-        <v>24.8584114840943</v>
+        <v>25.20366719915117</v>
       </c>
       <c r="N74">
-        <v>52.8825885159057</v>
+        <v>52.53733280084883</v>
       </c>
       <c r="O74">
-        <v>15.86477655477171</v>
+        <v>15.76119984025465</v>
       </c>
       <c r="P74">
-        <v>37.01781196113399</v>
+        <v>36.77613296059418</v>
       </c>
       <c r="Q74">
-        <v>60.31781196113398</v>
+        <v>60.07613296059418</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1772207006418843</v>
+        <v>0.1815666232821582</v>
       </c>
       <c r="T74">
-        <v>3.035120107202871</v>
+        <v>3.135487835615664</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.127351884481545</v>
+        <v>3.084511447707825</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08177808828618273</v>
+        <v>0.08162798039263784</v>
       </c>
       <c r="C75">
-        <v>170.0802912446102</v>
+        <v>165.2309294617147</v>
       </c>
       <c r="D75">
-        <v>510.5732272688094</v>
+        <v>511.110070088985</v>
       </c>
       <c r="E75">
-        <v>298.872475717077</v>
+        <v>304.2586803201482</v>
       </c>
       <c r="F75">
-        <v>393.1929360241991</v>
+        <v>398.5791406272704</v>
       </c>
       <c r="G75">
         <v>52.7</v>
@@ -7437,28 +7437,28 @@
         <v>77.741</v>
       </c>
       <c r="M75">
-        <v>25.20366719915117</v>
+        <v>25.54892291420803</v>
       </c>
       <c r="N75">
-        <v>52.53733280084883</v>
+        <v>52.19207708579196</v>
       </c>
       <c r="O75">
-        <v>15.76119984025465</v>
+        <v>15.65762312573759</v>
       </c>
       <c r="P75">
-        <v>36.77613296059418</v>
+        <v>36.53445396005438</v>
       </c>
       <c r="Q75">
-        <v>60.07613296059418</v>
+        <v>59.83445396005438</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1815666232821582</v>
+        <v>0.1862468476639917</v>
       </c>
       <c r="T75">
-        <v>3.135487835615664</v>
+        <v>3.243576158521749</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.084511447707825</v>
+        <v>3.042828860576638</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08162798039263784</v>
+        <v>0.08147787249909297</v>
       </c>
       <c r="C76">
-        <v>165.2309294617147</v>
+        <v>160.3826977951102</v>
       </c>
       <c r="D76">
-        <v>511.110070088985</v>
+        <v>511.6480430254518</v>
       </c>
       <c r="E76">
-        <v>304.2586803201482</v>
+        <v>309.6448849232195</v>
       </c>
       <c r="F76">
-        <v>398.5791406272704</v>
+        <v>403.9653452303416</v>
       </c>
       <c r="G76">
         <v>52.7</v>
@@ -7519,28 +7519,28 @@
         <v>77.741</v>
       </c>
       <c r="M76">
-        <v>25.54892291420803</v>
+        <v>25.8941786292649</v>
       </c>
       <c r="N76">
-        <v>52.19207708579196</v>
+        <v>51.8468213707351</v>
       </c>
       <c r="O76">
-        <v>15.65762312573759</v>
+        <v>15.55404641122053</v>
       </c>
       <c r="P76">
-        <v>36.53445396005438</v>
+        <v>36.29277495951457</v>
       </c>
       <c r="Q76">
-        <v>59.83445396005438</v>
+        <v>59.59277495951457</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1862468476639917</v>
+        <v>0.1913014899963719</v>
       </c>
       <c r="T76">
-        <v>3.243576158521749</v>
+        <v>3.360311547260321</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.042828860576638</v>
+        <v>3.002257809102284</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08147787249909297</v>
+        <v>0.0854773646055481</v>
       </c>
       <c r="C77">
-        <v>160.3826977951102</v>
+        <v>141.0390227004831</v>
       </c>
       <c r="D77">
-        <v>511.6480430254518</v>
+        <v>497.6905725338959</v>
       </c>
       <c r="E77">
-        <v>309.6448849232195</v>
+        <v>315.0310895262907</v>
       </c>
       <c r="F77">
-        <v>403.9653452303416</v>
+        <v>409.3515498334128</v>
       </c>
       <c r="G77">
         <v>52.7</v>
@@ -7601,45 +7601,45 @@
         <v>77.741</v>
       </c>
       <c r="M77">
-        <v>25.8941786292649</v>
+        <v>29.43237643302238</v>
       </c>
       <c r="N77">
-        <v>51.8468213707351</v>
+        <v>48.30862356697762</v>
       </c>
       <c r="O77">
-        <v>15.55404641122053</v>
+        <v>14.49258707009328</v>
       </c>
       <c r="P77">
-        <v>36.29277495951457</v>
+        <v>33.81603649688433</v>
       </c>
       <c r="Q77">
-        <v>59.59277495951457</v>
+        <v>57.11603649688433</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1913014899963719</v>
+        <v>0.1967773525231171</v>
       </c>
       <c r="T77">
-        <v>3.360311547260321</v>
+        <v>3.486774885060441</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.002257809102284</v>
+        <v>2.641342950234102</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0854773646055481</v>
+        <v>0.08538185671200321</v>
       </c>
       <c r="C78">
-        <v>141.0390227004831</v>
+        <v>135.9772415515416</v>
       </c>
       <c r="D78">
-        <v>497.6905725338959</v>
+        <v>498.0149959880256</v>
       </c>
       <c r="E78">
-        <v>315.0310895262907</v>
+        <v>320.4172941293619</v>
       </c>
       <c r="F78">
-        <v>409.3515498334128</v>
+        <v>414.7377544364841</v>
       </c>
       <c r="G78">
         <v>52.7</v>
@@ -7683,28 +7683,28 @@
         <v>77.741</v>
       </c>
       <c r="M78">
-        <v>29.43237643302238</v>
+        <v>29.81964454398321</v>
       </c>
       <c r="N78">
-        <v>48.30862356697762</v>
+        <v>47.9213554560168</v>
       </c>
       <c r="O78">
-        <v>14.49258707009328</v>
+        <v>14.37640663680504</v>
       </c>
       <c r="P78">
-        <v>33.81603649688433</v>
+        <v>33.54494881921176</v>
       </c>
       <c r="Q78">
-        <v>57.11603649688433</v>
+        <v>56.84494881921177</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1967773525231171</v>
+        <v>0.2027293770087097</v>
       </c>
       <c r="T78">
-        <v>3.486774885060441</v>
+        <v>3.62423503484318</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.641342950234102</v>
+        <v>2.607039795036257</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08538185671200321</v>
+        <v>0.08528634881845834</v>
       </c>
       <c r="C79">
-        <v>135.9772415515416</v>
+        <v>130.9158836343692</v>
       </c>
       <c r="D79">
-        <v>498.0149959880256</v>
+        <v>498.3398426739244</v>
       </c>
       <c r="E79">
-        <v>320.4172941293619</v>
+        <v>325.8034987324332</v>
       </c>
       <c r="F79">
-        <v>414.7377544364841</v>
+        <v>420.1239590395553</v>
       </c>
       <c r="G79">
         <v>52.7</v>
@@ -7765,28 +7765,28 @@
         <v>77.741</v>
       </c>
       <c r="M79">
-        <v>29.81964454398321</v>
+        <v>30.20691265494403</v>
       </c>
       <c r="N79">
-        <v>47.9213554560168</v>
+        <v>47.53408734505597</v>
       </c>
       <c r="O79">
-        <v>14.37640663680504</v>
+        <v>14.26022620351679</v>
       </c>
       <c r="P79">
-        <v>33.54494881921176</v>
+        <v>33.27386114153918</v>
       </c>
       <c r="Q79">
-        <v>56.84494881921177</v>
+        <v>56.57386114153918</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2027293770087097</v>
+        <v>0.2092224946293561</v>
       </c>
       <c r="T79">
-        <v>3.62423503484318</v>
+        <v>3.774191561878895</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.607039795036257</v>
+        <v>2.573616207920407</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08528634881845834</v>
+        <v>0.08519084092491347</v>
       </c>
       <c r="C80">
-        <v>130.9158836343692</v>
+        <v>125.854949777707</v>
       </c>
       <c r="D80">
-        <v>498.3398426739244</v>
+        <v>498.6651134203335</v>
       </c>
       <c r="E80">
-        <v>325.8034987324332</v>
+        <v>331.1897033355044</v>
       </c>
       <c r="F80">
-        <v>420.1239590395553</v>
+        <v>425.5101636426265</v>
       </c>
       <c r="G80">
         <v>52.7</v>
@@ -7847,28 +7847,28 @@
         <v>77.741</v>
       </c>
       <c r="M80">
-        <v>30.20691265494403</v>
+        <v>30.59418076590485</v>
       </c>
       <c r="N80">
-        <v>47.53408734505597</v>
+        <v>47.14681923409515</v>
       </c>
       <c r="O80">
-        <v>14.26022620351679</v>
+        <v>14.14404577022855</v>
       </c>
       <c r="P80">
-        <v>33.27386114153918</v>
+        <v>33.00277346386661</v>
       </c>
       <c r="Q80">
-        <v>56.57386114153918</v>
+        <v>56.30277346386661</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2092224946293561</v>
+        <v>0.2163340044043499</v>
       </c>
       <c r="T80">
-        <v>3.774191561878895</v>
+        <v>3.938429662918011</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.573616207920407</v>
+        <v>2.541038787566984</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08519084092491347</v>
+        <v>0.0850953330313686</v>
       </c>
       <c r="C81">
-        <v>125.854949777707</v>
+        <v>120.7944408124613</v>
       </c>
       <c r="D81">
-        <v>498.6651134203335</v>
+        <v>498.9908090581591</v>
       </c>
       <c r="E81">
-        <v>331.1897033355044</v>
+        <v>336.5759079385756</v>
       </c>
       <c r="F81">
-        <v>425.5101636426265</v>
+        <v>430.8963682456977</v>
       </c>
       <c r="G81">
         <v>52.7</v>
@@ -7929,28 +7929,28 @@
         <v>77.741</v>
       </c>
       <c r="M81">
-        <v>30.59418076590485</v>
+        <v>30.98144887686567</v>
       </c>
       <c r="N81">
-        <v>47.14681923409515</v>
+        <v>46.75955112313433</v>
       </c>
       <c r="O81">
-        <v>14.14404577022855</v>
+        <v>14.0278653369403</v>
       </c>
       <c r="P81">
-        <v>33.00277346386661</v>
+        <v>32.73168578619403</v>
       </c>
       <c r="Q81">
-        <v>56.30277346386661</v>
+        <v>56.03168578619403</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2163340044043499</v>
+        <v>0.224156665156843</v>
       </c>
       <c r="T81">
-        <v>3.938429662918011</v>
+        <v>4.11909157406104</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.541038787566984</v>
+        <v>2.509275802722397</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0850953330313686</v>
+        <v>0.08721112513782371</v>
       </c>
       <c r="C82">
-        <v>120.7944408124613</v>
+        <v>108.2913425961821</v>
       </c>
       <c r="D82">
-        <v>498.9908090581591</v>
+        <v>491.873915444951</v>
       </c>
       <c r="E82">
-        <v>336.5759079385756</v>
+        <v>341.9621125416468</v>
       </c>
       <c r="F82">
-        <v>430.8963682456977</v>
+        <v>436.282572848769</v>
       </c>
       <c r="G82">
         <v>52.7</v>
@@ -8011,45 +8011,45 @@
         <v>77.741</v>
       </c>
       <c r="M82">
-        <v>30.98144887686567</v>
+        <v>33.07021902193669</v>
       </c>
       <c r="N82">
-        <v>46.75955112313433</v>
+        <v>44.67078097806331</v>
       </c>
       <c r="O82">
-        <v>14.0278653369403</v>
+        <v>13.40123429341899</v>
       </c>
       <c r="P82">
-        <v>32.73168578619403</v>
+        <v>31.26954668464432</v>
       </c>
       <c r="Q82">
-        <v>56.03168578619403</v>
+        <v>54.56954668464432</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.224156665156843</v>
+        <v>0.2328027638832827</v>
       </c>
       <c r="T82">
-        <v>4.11909157406104</v>
+        <v>4.318770528482281</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.509275802722397</v>
+        <v>2.350785761304802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08721112513782371</v>
+        <v>0.08714291724427883</v>
       </c>
       <c r="C83">
-        <v>108.2913425961821</v>
+        <v>103.1314007605316</v>
       </c>
       <c r="D83">
-        <v>491.873915444951</v>
+        <v>492.1001782123717</v>
       </c>
       <c r="E83">
-        <v>341.9621125416468</v>
+        <v>347.3483171447181</v>
       </c>
       <c r="F83">
-        <v>436.282572848769</v>
+        <v>441.6687774518402</v>
       </c>
       <c r="G83">
         <v>52.7</v>
@@ -8093,28 +8093,28 @@
         <v>77.741</v>
       </c>
       <c r="M83">
-        <v>33.07021902193669</v>
+        <v>33.47849333084949</v>
       </c>
       <c r="N83">
-        <v>44.67078097806331</v>
+        <v>44.26250666915051</v>
       </c>
       <c r="O83">
-        <v>13.40123429341899</v>
+        <v>13.27875200074515</v>
       </c>
       <c r="P83">
-        <v>31.26954668464432</v>
+        <v>30.98375466840536</v>
       </c>
       <c r="Q83">
-        <v>54.56954668464432</v>
+        <v>54.28375466840536</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2328027638832827</v>
+        <v>0.2424095402459936</v>
       </c>
       <c r="T83">
-        <v>4.318770528482281</v>
+        <v>4.540636033394772</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.350785761304802</v>
+        <v>2.3221176422645</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08714291724427883</v>
+        <v>0.08707470935073397</v>
       </c>
       <c r="C84">
-        <v>103.1314007605316</v>
+        <v>97.97166718313122</v>
       </c>
       <c r="D84">
-        <v>492.1001782123717</v>
+        <v>492.3266492380426</v>
       </c>
       <c r="E84">
-        <v>347.3483171447181</v>
+        <v>352.7345217477893</v>
       </c>
       <c r="F84">
-        <v>441.6687774518402</v>
+        <v>447.0549820549114</v>
       </c>
       <c r="G84">
         <v>52.7</v>
@@ -8175,28 +8175,28 @@
         <v>77.741</v>
       </c>
       <c r="M84">
-        <v>33.47849333084949</v>
+        <v>33.88676763976229</v>
       </c>
       <c r="N84">
-        <v>44.26250666915051</v>
+        <v>43.85423236023771</v>
       </c>
       <c r="O84">
-        <v>13.27875200074515</v>
+        <v>13.15626970807131</v>
       </c>
       <c r="P84">
-        <v>30.98375466840536</v>
+        <v>30.6979626521664</v>
       </c>
       <c r="Q84">
-        <v>54.28375466840536</v>
+        <v>53.99796265216639</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2424095402459936</v>
+        <v>0.2531465255925528</v>
       </c>
       <c r="T84">
-        <v>4.540636033394772</v>
+        <v>4.788603362414615</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.3221176422645</v>
+        <v>2.294140321273361</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08707470935073397</v>
+        <v>0.08700650145718909</v>
       </c>
       <c r="C85">
-        <v>97.97166718313122</v>
+        <v>92.81214215164295</v>
       </c>
       <c r="D85">
-        <v>492.3266492380426</v>
+        <v>492.5533288096256</v>
       </c>
       <c r="E85">
-        <v>352.7345217477893</v>
+        <v>358.1207263508605</v>
       </c>
       <c r="F85">
-        <v>447.0549820549114</v>
+        <v>452.4411866579827</v>
       </c>
       <c r="G85">
         <v>52.7</v>
@@ -8257,28 +8257,28 @@
         <v>77.741</v>
       </c>
       <c r="M85">
-        <v>33.88676763976229</v>
+        <v>34.29504194867508</v>
       </c>
       <c r="N85">
-        <v>43.85423236023771</v>
+        <v>43.44595805132492</v>
       </c>
       <c r="O85">
-        <v>13.15626970807131</v>
+        <v>13.03378741539747</v>
       </c>
       <c r="P85">
-        <v>30.6979626521664</v>
+        <v>30.41217063592744</v>
       </c>
       <c r="Q85">
-        <v>53.99796265216639</v>
+        <v>53.71217063592744</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2531465255925528</v>
+        <v>0.2652256341074319</v>
       </c>
       <c r="T85">
-        <v>4.788603362414615</v>
+        <v>5.067566607561939</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.294140321273361</v>
+        <v>2.266829126972488</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08700650145718908</v>
+        <v>0.08693829356364421</v>
       </c>
       <c r="C86">
-        <v>92.812142151643</v>
+        <v>87.65282595425901</v>
       </c>
       <c r="D86">
-        <v>492.5533288096256</v>
+        <v>492.7802172153127</v>
       </c>
       <c r="E86">
-        <v>358.1207263508605</v>
+        <v>363.5069309539317</v>
       </c>
       <c r="F86">
-        <v>452.4411866579826</v>
+        <v>457.8273912610538</v>
       </c>
       <c r="G86">
         <v>52.7</v>
@@ -8339,28 +8339,28 @@
         <v>77.741</v>
       </c>
       <c r="M86">
-        <v>34.29504194867508</v>
+        <v>34.70331625758788</v>
       </c>
       <c r="N86">
-        <v>43.44595805132492</v>
+        <v>43.03768374241212</v>
       </c>
       <c r="O86">
-        <v>13.03378741539747</v>
+        <v>12.91130512272364</v>
       </c>
       <c r="P86">
-        <v>30.41217063592744</v>
+        <v>30.12637861968848</v>
       </c>
       <c r="Q86">
-        <v>53.71217063592744</v>
+        <v>53.42637861968849</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2652256341074317</v>
+        <v>0.2789152904242947</v>
       </c>
       <c r="T86">
-        <v>5.067566607561935</v>
+        <v>5.383724952062234</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.266829126972488</v>
+        <v>2.240160549008106</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08693829356364421</v>
+        <v>0.08687008567009932</v>
       </c>
       <c r="C87">
-        <v>87.65282595425901</v>
+        <v>82.4937188797025</v>
       </c>
       <c r="D87">
-        <v>492.7802172153127</v>
+        <v>493.0073147438275</v>
       </c>
       <c r="E87">
-        <v>363.5069309539317</v>
+        <v>368.8931355570029</v>
       </c>
       <c r="F87">
-        <v>457.8273912610538</v>
+        <v>463.213595864125</v>
       </c>
       <c r="G87">
         <v>52.7</v>
@@ -8421,28 +8421,28 @@
         <v>77.741</v>
       </c>
       <c r="M87">
-        <v>34.70331625758788</v>
+        <v>35.11159056650068</v>
       </c>
       <c r="N87">
-        <v>43.03768374241212</v>
+        <v>42.62940943349932</v>
       </c>
       <c r="O87">
-        <v>12.91130512272364</v>
+        <v>12.7888228300498</v>
       </c>
       <c r="P87">
-        <v>30.12637861968848</v>
+        <v>29.84058660344952</v>
       </c>
       <c r="Q87">
-        <v>53.42637861968849</v>
+        <v>53.14058660344952</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2789152904242947</v>
+        <v>0.2945606119292809</v>
       </c>
       <c r="T87">
-        <v>5.383724952062234</v>
+        <v>5.74504877434829</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.240160549008106</v>
+        <v>2.214112170531267</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08687008567009932</v>
+        <v>0.08680187777655446</v>
       </c>
       <c r="C88">
-        <v>82.4937188797025</v>
+        <v>77.33482121722921</v>
       </c>
       <c r="D88">
-        <v>493.0073147438275</v>
+        <v>493.2346216844255</v>
       </c>
       <c r="E88">
-        <v>368.8931355570029</v>
+        <v>374.2793401600741</v>
       </c>
       <c r="F88">
-        <v>463.213595864125</v>
+        <v>468.5998004671962</v>
       </c>
       <c r="G88">
         <v>52.7</v>
@@ -8503,28 +8503,28 @@
         <v>77.741</v>
       </c>
       <c r="M88">
-        <v>35.11159056650068</v>
+        <v>35.51986487541348</v>
       </c>
       <c r="N88">
-        <v>42.62940943349932</v>
+        <v>42.22113512458652</v>
       </c>
       <c r="O88">
-        <v>12.7888228300498</v>
+        <v>12.66634053737596</v>
       </c>
       <c r="P88">
-        <v>29.84058660344952</v>
+        <v>29.55479458721057</v>
       </c>
       <c r="Q88">
-        <v>53.14058660344952</v>
+        <v>52.85479458721056</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2945606119292809</v>
+        <v>0.3126129059734958</v>
       </c>
       <c r="T88">
-        <v>5.74504877434829</v>
+        <v>6.161960876986047</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.214112170531267</v>
+        <v>2.188662605352747</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08680187777655446</v>
+        <v>0.08673366988300958</v>
       </c>
       <c r="C89">
-        <v>77.33482121722921</v>
+        <v>72.1761332566287</v>
       </c>
       <c r="D89">
-        <v>493.2346216844255</v>
+        <v>493.4621383268962</v>
       </c>
       <c r="E89">
-        <v>374.2793401600741</v>
+        <v>379.6655447631454</v>
       </c>
       <c r="F89">
-        <v>468.5998004671962</v>
+        <v>473.9860050702675</v>
       </c>
       <c r="G89">
         <v>52.7</v>
@@ -8585,28 +8585,28 @@
         <v>77.741</v>
       </c>
       <c r="M89">
-        <v>35.51986487541348</v>
+        <v>35.92813918432628</v>
       </c>
       <c r="N89">
-        <v>42.22113512458652</v>
+        <v>41.81286081567372</v>
       </c>
       <c r="O89">
-        <v>12.66634053737596</v>
+        <v>12.54385824470212</v>
       </c>
       <c r="P89">
-        <v>29.55479458721057</v>
+        <v>29.26900257097161</v>
       </c>
       <c r="Q89">
-        <v>52.85479458721056</v>
+        <v>52.56900257097161</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3126129059734958</v>
+        <v>0.3336739156917465</v>
       </c>
       <c r="T89">
-        <v>6.161960876986047</v>
+        <v>6.648358330063432</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.188662605352747</v>
+        <v>2.163791439382829</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08673366988300958</v>
+        <v>0.0866654619894647</v>
       </c>
       <c r="C90">
-        <v>72.1761332566287</v>
+        <v>67.01765528822534</v>
       </c>
       <c r="D90">
-        <v>493.4621383268962</v>
+        <v>493.6898649615641</v>
       </c>
       <c r="E90">
-        <v>379.6655447631454</v>
+        <v>385.0517493662166</v>
       </c>
       <c r="F90">
-        <v>473.9860050702675</v>
+        <v>479.3722096733387</v>
       </c>
       <c r="G90">
         <v>52.7</v>
@@ -8667,28 +8667,28 @@
         <v>77.741</v>
       </c>
       <c r="M90">
-        <v>35.92813918432628</v>
+        <v>36.33641349323908</v>
       </c>
       <c r="N90">
-        <v>41.81286081567372</v>
+        <v>41.40458650676092</v>
       </c>
       <c r="O90">
-        <v>12.54385824470212</v>
+        <v>12.42137595202828</v>
       </c>
       <c r="P90">
-        <v>29.26900257097161</v>
+        <v>28.98321055473264</v>
       </c>
       <c r="Q90">
-        <v>52.56900257097161</v>
+        <v>52.28321055473265</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3336739156917465</v>
+        <v>0.3585641999042246</v>
       </c>
       <c r="T90">
-        <v>6.648358330063432</v>
+        <v>7.223191683700339</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.163791439382829</v>
+        <v>2.139479176018978</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0866654619894647</v>
+        <v>0.08659725409591983</v>
       </c>
       <c r="C91">
-        <v>67.01765528822534</v>
+        <v>61.85938760287974</v>
       </c>
       <c r="D91">
-        <v>493.6898649615641</v>
+        <v>493.9178018792897</v>
       </c>
       <c r="E91">
-        <v>385.0517493662166</v>
+        <v>390.4379539692878</v>
       </c>
       <c r="F91">
-        <v>479.3722096733387</v>
+        <v>484.75841427641</v>
       </c>
       <c r="G91">
         <v>52.7</v>
@@ -8749,28 +8749,28 @@
         <v>77.741</v>
       </c>
       <c r="M91">
-        <v>36.33641349323908</v>
+        <v>36.74468780215188</v>
       </c>
       <c r="N91">
-        <v>41.40458650676092</v>
+        <v>40.99631219784812</v>
       </c>
       <c r="O91">
-        <v>12.42137595202828</v>
+        <v>12.29889365935444</v>
       </c>
       <c r="P91">
-        <v>28.98321055473264</v>
+        <v>28.69741853849369</v>
       </c>
       <c r="Q91">
-        <v>52.28321055473265</v>
+        <v>51.99741853849369</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3585641999042246</v>
+        <v>0.3884325409591983</v>
       </c>
       <c r="T91">
-        <v>7.223191683700339</v>
+        <v>7.912991708064628</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.139479176018978</v>
+        <v>2.115707185174322</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08659725409591983</v>
+        <v>0.08652904620237495</v>
       </c>
       <c r="C92">
-        <v>61.85938760287974</v>
+        <v>56.70133049198995</v>
       </c>
       <c r="D92">
-        <v>493.9178018792897</v>
+        <v>494.1459493714711</v>
       </c>
       <c r="E92">
-        <v>390.4379539692878</v>
+        <v>395.824158572359</v>
       </c>
       <c r="F92">
-        <v>484.75841427641</v>
+        <v>490.1446188794811</v>
       </c>
       <c r="G92">
         <v>52.7</v>
@@ -8831,28 +8831,28 @@
         <v>77.741</v>
       </c>
       <c r="M92">
-        <v>36.74468780215188</v>
+        <v>37.15296211106467</v>
       </c>
       <c r="N92">
-        <v>40.99631219784812</v>
+        <v>40.58803788893533</v>
       </c>
       <c r="O92">
-        <v>12.29889365935444</v>
+        <v>12.1764113666806</v>
       </c>
       <c r="P92">
-        <v>28.69741853849369</v>
+        <v>28.41162652225473</v>
       </c>
       <c r="Q92">
-        <v>51.99741853849369</v>
+        <v>51.71162652225473</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3884325409591983</v>
+        <v>0.4249382911374995</v>
       </c>
       <c r="T92">
-        <v>7.912991708064628</v>
+        <v>8.756080626732093</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.115707185174322</v>
+        <v>2.092457655666912</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08652904620237495</v>
+        <v>0.08646083830883008</v>
       </c>
       <c r="C93">
-        <v>56.70133049198995</v>
+        <v>51.54348424749242</v>
       </c>
       <c r="D93">
-        <v>494.1459493714711</v>
+        <v>494.3743077300448</v>
       </c>
       <c r="E93">
-        <v>395.824158572359</v>
+        <v>401.2103631754302</v>
       </c>
       <c r="F93">
-        <v>490.1446188794811</v>
+        <v>495.5308234825524</v>
       </c>
       <c r="G93">
         <v>52.7</v>
@@ -8913,28 +8913,28 @@
         <v>77.741</v>
       </c>
       <c r="M93">
-        <v>37.15296211106467</v>
+        <v>37.56123641997747</v>
       </c>
       <c r="N93">
-        <v>40.58803788893533</v>
+        <v>40.17976358002253</v>
       </c>
       <c r="O93">
-        <v>12.1764113666806</v>
+        <v>12.05392907400676</v>
       </c>
       <c r="P93">
-        <v>28.41162652225473</v>
+        <v>28.12583450601577</v>
       </c>
       <c r="Q93">
-        <v>51.71162652225473</v>
+        <v>51.42583450601578</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4249382911374995</v>
+        <v>0.4705704788603762</v>
       </c>
       <c r="T93">
-        <v>8.756080626732093</v>
+        <v>9.809941775066426</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.092457655666912</v>
+        <v>2.069713550714011</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08646083830883008</v>
+        <v>0.08639263041528519</v>
       </c>
       <c r="C94">
-        <v>51.54348424749242</v>
+        <v>46.38584916186386</v>
       </c>
       <c r="D94">
-        <v>494.3743077300448</v>
+        <v>494.6028772474875</v>
       </c>
       <c r="E94">
-        <v>401.2103631754302</v>
+        <v>406.5965677785015</v>
       </c>
       <c r="F94">
-        <v>495.5308234825524</v>
+        <v>500.9170280856236</v>
       </c>
       <c r="G94">
         <v>52.7</v>
@@ -8995,28 +8995,28 @@
         <v>77.741</v>
       </c>
       <c r="M94">
-        <v>37.56123641997747</v>
+        <v>37.96951072889027</v>
       </c>
       <c r="N94">
-        <v>40.17976358002253</v>
+        <v>39.77148927110973</v>
       </c>
       <c r="O94">
-        <v>12.05392907400676</v>
+        <v>11.93144678133292</v>
       </c>
       <c r="P94">
-        <v>28.12583450601577</v>
+        <v>27.84004248977681</v>
       </c>
       <c r="Q94">
-        <v>51.42583450601578</v>
+        <v>51.14004248977682</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4705704788603762</v>
+        <v>0.5292404345040745</v>
       </c>
       <c r="T94">
-        <v>9.809941775066426</v>
+        <v>11.16490610863914</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.069713550714011</v>
+        <v>2.047458566297731</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08639263041528519</v>
+        <v>0.08632442252174033</v>
       </c>
       <c r="C95">
-        <v>46.38584916186386</v>
+        <v>41.22842552812187</v>
       </c>
       <c r="D95">
-        <v>494.6028772474875</v>
+        <v>494.8316582168167</v>
       </c>
       <c r="E95">
-        <v>406.5965677785015</v>
+        <v>411.9827723815727</v>
       </c>
       <c r="F95">
-        <v>500.9170280856236</v>
+        <v>506.3032326886948</v>
       </c>
       <c r="G95">
         <v>52.7</v>
@@ -9077,28 +9077,28 @@
         <v>77.741</v>
       </c>
       <c r="M95">
-        <v>37.96951072889027</v>
+        <v>38.37778503780307</v>
       </c>
       <c r="N95">
-        <v>39.77148927110973</v>
+        <v>39.36321496219693</v>
       </c>
       <c r="O95">
-        <v>11.93144678133292</v>
+        <v>11.80896448865908</v>
       </c>
       <c r="P95">
-        <v>27.84004248977681</v>
+        <v>27.55425047353785</v>
       </c>
       <c r="Q95">
-        <v>51.14004248977682</v>
+        <v>50.85425047353785</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5292404345040745</v>
+        <v>0.6074670420290059</v>
       </c>
       <c r="T95">
-        <v>11.16490610863914</v>
+        <v>12.97152522006942</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.047458566297731</v>
+        <v>2.025677092188181</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08632442252174033</v>
+        <v>0.08625621462819545</v>
       </c>
       <c r="C96">
-        <v>41.22842552812187</v>
+        <v>36.07121363982668</v>
       </c>
       <c r="D96">
-        <v>494.8316582168167</v>
+        <v>495.0606509315927</v>
       </c>
       <c r="E96">
-        <v>411.9827723815727</v>
+        <v>417.368976984644</v>
       </c>
       <c r="F96">
-        <v>506.3032326886948</v>
+        <v>511.6894372917661</v>
       </c>
       <c r="G96">
         <v>52.7</v>
@@ -9159,28 +9159,28 @@
         <v>77.741</v>
       </c>
       <c r="M96">
-        <v>38.37778503780307</v>
+        <v>38.78605934671587</v>
       </c>
       <c r="N96">
-        <v>39.36321496219693</v>
+        <v>38.95494065328413</v>
       </c>
       <c r="O96">
-        <v>11.80896448865908</v>
+        <v>11.68648219598524</v>
       </c>
       <c r="P96">
-        <v>27.55425047353785</v>
+        <v>27.26845845729889</v>
       </c>
       <c r="Q96">
-        <v>50.85425047353785</v>
+        <v>50.56845845729889</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6074670420290059</v>
+        <v>0.7169842925639098</v>
       </c>
       <c r="T96">
-        <v>12.97152522006942</v>
+        <v>15.50079197607182</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.025677092188181</v>
+        <v>2.004354175428305</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08625621462819545</v>
+        <v>0.09573040673465057</v>
       </c>
       <c r="C97">
-        <v>36.07121363982668</v>
+        <v>0.7847813843587801</v>
       </c>
       <c r="D97">
-        <v>495.0606509315927</v>
+        <v>465.160423279196</v>
       </c>
       <c r="E97">
-        <v>417.368976984644</v>
+        <v>422.7551815877152</v>
       </c>
       <c r="F97">
-        <v>511.6894372917661</v>
+        <v>517.0756418948373</v>
       </c>
       <c r="G97">
         <v>52.7</v>
@@ -9241,45 +9241,45 @@
         <v>77.741</v>
       </c>
       <c r="M97">
-        <v>38.78605934671587</v>
+        <v>46.53680777053535</v>
       </c>
       <c r="N97">
-        <v>38.95494065328413</v>
+        <v>31.20419222946465</v>
       </c>
       <c r="O97">
-        <v>11.68648219598524</v>
+        <v>9.361257668839393</v>
       </c>
       <c r="P97">
-        <v>27.26845845729889</v>
+        <v>21.84293456062525</v>
       </c>
       <c r="Q97">
-        <v>50.56845845729889</v>
+        <v>45.14293456062525</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7169842925639098</v>
+        <v>0.8812601683662658</v>
       </c>
       <c r="T97">
-        <v>15.50079197607182</v>
+        <v>19.29469211007543</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.3</v>
       </c>
       <c r="W97">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.004354175428305</v>
+        <v>1.670527131627225</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09573040673465058</v>
+        <v>0.0957615988411057</v>
       </c>
       <c r="C98">
-        <v>0.7847813843587801</v>
+        <v>-4.693900491096315</v>
       </c>
       <c r="D98">
-        <v>465.160423279196</v>
+        <v>465.0679460068122</v>
       </c>
       <c r="E98">
-        <v>422.7551815877151</v>
+        <v>428.1413861907864</v>
       </c>
       <c r="F98">
-        <v>517.0756418948372</v>
+        <v>522.4618464979085</v>
       </c>
       <c r="G98">
         <v>52.7</v>
@@ -9323,28 +9323,28 @@
         <v>77.741</v>
       </c>
       <c r="M98">
-        <v>46.53680777053535</v>
+        <v>47.02156618481176</v>
       </c>
       <c r="N98">
-        <v>31.20419222946465</v>
+        <v>30.71943381518824</v>
       </c>
       <c r="O98">
-        <v>9.361257668839395</v>
+        <v>9.215830144556472</v>
       </c>
       <c r="P98">
-        <v>21.84293456062526</v>
+        <v>21.50360367063177</v>
       </c>
       <c r="Q98">
-        <v>45.14293456062526</v>
+        <v>44.80360367063177</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8812601683662635</v>
+        <v>1.155053294703522</v>
       </c>
       <c r="T98">
-        <v>19.29469211007537</v>
+        <v>25.61785900008135</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.670527131627226</v>
+        <v>1.653305202435192</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0957615988411057</v>
+        <v>0.09579279094756082</v>
       </c>
       <c r="C99">
-        <v>-4.693900491096315</v>
+        <v>-10.17254560355252</v>
       </c>
       <c r="D99">
-        <v>465.0679460068122</v>
+        <v>464.9755054974272</v>
       </c>
       <c r="E99">
-        <v>428.1413861907864</v>
+        <v>433.5275907938575</v>
       </c>
       <c r="F99">
-        <v>522.4618464979085</v>
+        <v>527.8480511009797</v>
       </c>
       <c r="G99">
         <v>52.7</v>
@@ -9405,28 +9405,28 @@
         <v>77.741</v>
       </c>
       <c r="M99">
-        <v>47.02156618481176</v>
+        <v>47.50632459908817</v>
       </c>
       <c r="N99">
-        <v>30.71943381518824</v>
+        <v>30.23467540091183</v>
       </c>
       <c r="O99">
-        <v>9.215830144556472</v>
+        <v>9.070402620273549</v>
       </c>
       <c r="P99">
-        <v>21.50360367063177</v>
+        <v>21.16427278063829</v>
       </c>
       <c r="Q99">
-        <v>44.80360367063177</v>
+        <v>44.46427278063828</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.155053294703522</v>
+        <v>1.70263954737804</v>
       </c>
       <c r="T99">
-        <v>25.61785900008135</v>
+        <v>38.2641927800933</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.653305202435192</v>
+        <v>1.636434741185854</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09579279094756082</v>
+        <v>0.09582398305401595</v>
       </c>
       <c r="C100">
-        <v>-10.17254560355252</v>
+        <v>-15.65115397492764</v>
       </c>
       <c r="D100">
-        <v>464.9755054974272</v>
+        <v>464.8831017291233</v>
       </c>
       <c r="E100">
-        <v>433.5275907938575</v>
+        <v>438.9137953969288</v>
       </c>
       <c r="F100">
-        <v>527.8480511009797</v>
+        <v>533.234255704051</v>
       </c>
       <c r="G100">
         <v>52.7</v>
@@ -9487,28 +9487,28 @@
         <v>77.741</v>
       </c>
       <c r="M100">
-        <v>47.50632459908817</v>
+        <v>47.99108301336459</v>
       </c>
       <c r="N100">
-        <v>30.23467540091183</v>
+        <v>29.74991698663541</v>
       </c>
       <c r="O100">
-        <v>9.070402620273549</v>
+        <v>8.924975095990623</v>
       </c>
       <c r="P100">
-        <v>21.16427278063829</v>
+        <v>20.82494189064479</v>
       </c>
       <c r="Q100">
-        <v>44.46427278063828</v>
+        <v>44.12494189064479</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.70263954737804</v>
+        <v>3.345398305401591</v>
       </c>
       <c r="T100">
-        <v>38.2641927800933</v>
+        <v>76.20319412012915</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.636434741185854</v>
+        <v>1.619905097335491</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09582398305401595</v>
-      </c>
-      <c r="C101">
-        <v>-15.65115397492764</v>
-      </c>
-      <c r="D101">
-        <v>464.8831017291233</v>
-      </c>
-      <c r="E101">
-        <v>438.9137953969288</v>
-      </c>
-      <c r="F101">
-        <v>533.234255704051</v>
-      </c>
-      <c r="G101">
-        <v>52.7</v>
-      </c>
-      <c r="H101">
-        <v>444.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>101.041</v>
-      </c>
-      <c r="K101">
-        <v>23.3</v>
-      </c>
-      <c r="L101">
-        <v>77.741</v>
-      </c>
-      <c r="M101">
-        <v>47.99108301336459</v>
-      </c>
-      <c r="N101">
-        <v>29.74991698663541</v>
-      </c>
-      <c r="O101">
-        <v>8.924975095990623</v>
-      </c>
-      <c r="P101">
-        <v>20.82494189064479</v>
-      </c>
-      <c r="Q101">
-        <v>44.12494189064479</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.345398305401591</v>
-      </c>
-      <c r="T101">
-        <v>76.20319412012915</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.619905097335491</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
